--- a/data/source/weekly/cs-en-us-121pct.xlsx
+++ b/data/source/weekly/cs-en-us-121pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">6</t>
+      <t xml:space="preserve">7</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">2/2/2026</t>
+      <t xml:space="preserve">2/9/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">2/8/2026</t>
+      <t xml:space="preserve">2/15/2026</t>
     </r>
   </si>
   <si>
@@ -906,7 +906,7 @@
         <v>22</v>
       </c>
       <c r="C15" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D15" s="13" t="s">
         <v>20</v>
@@ -915,22 +915,22 @@
         <v>21</v>
       </c>
       <c r="F15" s="14">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G15" s="14">
         <v>2</v>
       </c>
       <c r="H15" s="15">
-        <v>-50</v>
+        <v>50</v>
       </c>
       <c r="I15" s="14">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="J15" s="14">
         <v>3</v>
       </c>
       <c r="K15" s="15">
-        <v>0</v>
+        <v>66.666666666666</v>
       </c>
       <c r="L15" s="13" t="s">
         <v>21</v>
@@ -956,25 +956,25 @@
         <v>-100</v>
       </c>
       <c r="F16" s="14">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G16" s="14">
         <v>5</v>
       </c>
       <c r="H16" s="15">
-        <v>-20</v>
+        <v>-40</v>
       </c>
       <c r="I16" s="14">
         <v>8</v>
       </c>
       <c r="J16" s="14">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K16" s="15">
-        <v>60</v>
+        <v>33.333333333333</v>
       </c>
       <c r="L16" s="15">
-        <v>14.285714285714</v>
+        <v>0</v>
       </c>
       <c r="M16" s="13" t="s">
         <v>21</v>
@@ -988,34 +988,34 @@
         <v>24</v>
       </c>
       <c r="C17" s="14">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="D17" s="14">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E17" s="15">
-        <v>83.333333333333</v>
+        <v>-80</v>
       </c>
       <c r="F17" s="14">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G17" s="14">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H17" s="15">
-        <v>50</v>
+        <v>35.294117647058</v>
       </c>
       <c r="I17" s="14">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="J17" s="14">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="K17" s="15">
-        <v>40.909090909090</v>
+        <v>18.518518518518</v>
       </c>
       <c r="L17" s="15">
-        <v>106.666666666667</v>
+        <v>60</v>
       </c>
       <c r="M17" s="13" t="s">
         <v>21</v>
@@ -1028,35 +1028,35 @@
       <c r="A18" s="13" t="s">
         <v>25</v>
       </c>
-      <c r="C18" s="13" t="s">
-        <v>20</v>
+      <c r="C18" s="14">
+        <v>2</v>
       </c>
       <c r="D18" s="14">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="E18" s="15">
-        <v>-100</v>
+        <v>-75</v>
       </c>
       <c r="F18" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G18" s="14">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="H18" s="15">
-        <v>-83.333333333333</v>
+        <v>-84.615384615384</v>
       </c>
       <c r="I18" s="14">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="J18" s="14">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="K18" s="15">
-        <v>-66.666666666666</v>
+        <v>-70.588235294117</v>
       </c>
       <c r="L18" s="15">
-        <v>-62.5</v>
+        <v>-37.5</v>
       </c>
       <c r="M18" s="13" t="s">
         <v>21</v>
@@ -1070,34 +1070,34 @@
         <v>26</v>
       </c>
       <c r="C19" s="14">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D19" s="14">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E19" s="15">
-        <v>-25</v>
+        <v>-16.666666666666</v>
       </c>
       <c r="F19" s="14">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="G19" s="14">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="H19" s="15">
-        <v>28.571428571428</v>
+        <v>16.666666666666</v>
       </c>
       <c r="I19" s="14">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="J19" s="14">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="K19" s="15">
-        <v>-8.108108108108</v>
+        <v>-9.302325581395</v>
       </c>
       <c r="L19" s="15">
-        <v>-12.820512820512</v>
+        <v>-18.75</v>
       </c>
       <c r="M19" s="13" t="s">
         <v>21</v>
@@ -1110,35 +1110,35 @@
       <c r="A20" s="13" t="s">
         <v>27</v>
       </c>
-      <c r="C20" s="13" t="s">
-        <v>20</v>
+      <c r="C20" s="14">
+        <v>2</v>
       </c>
       <c r="D20" s="14">
         <v>2</v>
       </c>
       <c r="E20" s="15">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="F20" s="14">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G20" s="14">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="H20" s="15">
-        <v>-92.857142857142</v>
+        <v>-66.666666666666</v>
       </c>
       <c r="I20" s="14">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="J20" s="14">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="K20" s="15">
-        <v>-57.142857142857</v>
+        <v>-50</v>
       </c>
       <c r="L20" s="15">
-        <v>100</v>
+        <v>166.666666666667</v>
       </c>
       <c r="M20" s="13" t="s">
         <v>21</v>
@@ -1152,34 +1152,34 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="D21" s="17">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="E21" s="18">
-        <v>7.142857142857</v>
+        <v>-45.454545454545</v>
       </c>
       <c r="F21" s="17">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="G21" s="17">
         <v>64</v>
       </c>
       <c r="H21" s="18">
-        <v>-9.375</v>
+        <v>-14.0625</v>
       </c>
       <c r="I21" s="17">
-        <v>85</v>
+        <v>97</v>
       </c>
       <c r="J21" s="17">
-        <v>90</v>
+        <v>112</v>
       </c>
       <c r="K21" s="18">
-        <v>-5.555555555555</v>
+        <v>-13.392857142857</v>
       </c>
       <c r="L21" s="18">
-        <v>18.055555555555</v>
+        <v>11.494252873563</v>
       </c>
       <c r="M21" s="19" t="s">
         <v>21</v>
@@ -1246,7 +1246,7 @@
         <v>20</v>
       </c>
       <c r="G23" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H23" s="15">
         <v>-100</v>
@@ -1255,7 +1255,7 @@
         <v>20</v>
       </c>
       <c r="J23" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K23" s="15">
         <v>-100</v>
@@ -1275,34 +1275,34 @@
         <v>31</v>
       </c>
       <c r="C24" s="14">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="D24" s="14">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="E24" s="15">
-        <v>-40.540540540540</v>
+        <v>-42.857142857142</v>
       </c>
       <c r="F24" s="14">
-        <v>82</v>
+        <v>73</v>
       </c>
       <c r="G24" s="14">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="H24" s="15">
-        <v>-38.805970149253</v>
+        <v>-44.696969696969</v>
       </c>
       <c r="I24" s="14">
-        <v>107</v>
+        <v>127</v>
       </c>
       <c r="J24" s="14">
-        <v>168</v>
+        <v>203</v>
       </c>
       <c r="K24" s="15">
-        <v>-36.309523809523</v>
+        <v>-37.438423645320</v>
       </c>
       <c r="L24" s="15">
-        <v>-36.309523809523</v>
+        <v>-38.349514563106</v>
       </c>
       <c r="M24" s="13" t="s">
         <v>21</v>
@@ -1316,34 +1316,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="14">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="D25" s="14">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="E25" s="15">
-        <v>-36.363636363636</v>
+        <v>-55.555555555555</v>
       </c>
       <c r="F25" s="14">
-        <v>67</v>
+        <v>53</v>
       </c>
       <c r="G25" s="14">
-        <v>87</v>
+        <v>93</v>
       </c>
       <c r="H25" s="15">
-        <v>-22.988505747126</v>
+        <v>-43.010752688172</v>
       </c>
       <c r="I25" s="14">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="J25" s="14">
-        <v>113</v>
+        <v>140</v>
       </c>
       <c r="K25" s="15">
-        <v>-26.548672566371</v>
+        <v>-32.142857142857</v>
       </c>
       <c r="L25" s="15">
-        <v>-18.627450980392</v>
+        <v>-29.629629629629</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1360,31 +1360,31 @@
         <v>10</v>
       </c>
       <c r="D26" s="14">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E26" s="15">
-        <v>25</v>
+        <v>66.666666666666</v>
       </c>
       <c r="F26" s="14">
         <v>36</v>
       </c>
       <c r="G26" s="14">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="H26" s="15">
-        <v>12.5</v>
+        <v>28.571428571428</v>
       </c>
       <c r="I26" s="14">
+        <v>60</v>
+      </c>
+      <c r="J26" s="14">
         <v>50</v>
       </c>
-      <c r="J26" s="14">
-        <v>44</v>
-      </c>
       <c r="K26" s="15">
-        <v>13.636363636363</v>
+        <v>20</v>
       </c>
       <c r="L26" s="15">
-        <v>-3.846153846153</v>
+        <v>-1.639344262295</v>
       </c>
       <c r="M26" s="13" t="s">
         <v>21</v>
@@ -1407,25 +1407,25 @@
         <v>21</v>
       </c>
       <c r="F27" s="14">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G27" s="14">
         <v>2</v>
       </c>
       <c r="H27" s="15">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I27" s="14">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="J27" s="14">
         <v>3</v>
       </c>
       <c r="K27" s="15">
-        <v>33.333333333333</v>
+        <v>100</v>
       </c>
       <c r="L27" s="15">
-        <v>300</v>
+        <v>500</v>
       </c>
       <c r="M27" s="13" t="s">
         <v>21</v>
@@ -1448,25 +1448,25 @@
         <v>-50</v>
       </c>
       <c r="F28" s="14">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G28" s="14">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="H28" s="15">
-        <v>0</v>
+        <v>-66.666666666666</v>
       </c>
       <c r="I28" s="14">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J28" s="14">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="K28" s="15">
-        <v>-14.285714285714</v>
+        <v>-22.222222222222</v>
       </c>
       <c r="L28" s="15">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>

--- a/data/source/weekly/cs-en-us-121pct.xlsx
+++ b/data/source/weekly/cs-en-us-121pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">7</t>
+      <t xml:space="preserve">8</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">2/9/2026</t>
+      <t xml:space="preserve">2/16/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">2/15/2026</t>
+      <t xml:space="preserve">2/22/2026</t>
     </r>
   </si>
   <si>
@@ -905,8 +905,8 @@
       <c r="A15" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="C15" s="14">
-        <v>2</v>
+      <c r="C15" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D15" s="13" t="s">
         <v>20</v>
@@ -918,10 +918,10 @@
         <v>3</v>
       </c>
       <c r="G15" s="14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H15" s="15">
-        <v>50</v>
+        <v>200</v>
       </c>
       <c r="I15" s="14">
         <v>5</v>
@@ -950,31 +950,31 @@
         <v>20</v>
       </c>
       <c r="D16" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E16" s="15">
         <v>-100</v>
       </c>
       <c r="F16" s="14">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G16" s="14">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H16" s="15">
-        <v>-40</v>
+        <v>-75</v>
       </c>
       <c r="I16" s="14">
         <v>8</v>
       </c>
       <c r="J16" s="14">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="K16" s="15">
-        <v>33.333333333333</v>
+        <v>0</v>
       </c>
       <c r="L16" s="15">
-        <v>0</v>
+        <v>-20</v>
       </c>
       <c r="M16" s="13" t="s">
         <v>21</v>
@@ -988,34 +988,34 @@
         <v>24</v>
       </c>
       <c r="C17" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D17" s="14">
+        <v>3</v>
+      </c>
+      <c r="E17" s="15">
+        <v>-33.333333333333</v>
+      </c>
+      <c r="F17" s="14">
+        <v>21</v>
+      </c>
+      <c r="G17" s="14">
+        <v>20</v>
+      </c>
+      <c r="H17" s="15">
         <v>5</v>
       </c>
-      <c r="E17" s="15">
-        <v>-80</v>
-      </c>
-      <c r="F17" s="14">
-        <v>23</v>
-      </c>
-      <c r="G17" s="14">
-        <v>17</v>
-      </c>
-      <c r="H17" s="15">
-        <v>35.294117647058</v>
-      </c>
       <c r="I17" s="14">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="J17" s="14">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="K17" s="15">
-        <v>18.518518518518</v>
+        <v>16.666666666666</v>
       </c>
       <c r="L17" s="15">
-        <v>60</v>
+        <v>45.833333333333</v>
       </c>
       <c r="M17" s="13" t="s">
         <v>21</v>
@@ -1029,34 +1029,34 @@
         <v>25</v>
       </c>
       <c r="C18" s="14">
+        <v>1</v>
+      </c>
+      <c r="D18" s="14">
         <v>2</v>
       </c>
-      <c r="D18" s="14">
-        <v>8</v>
-      </c>
       <c r="E18" s="15">
+        <v>-50</v>
+      </c>
+      <c r="F18" s="14">
+        <v>3</v>
+      </c>
+      <c r="G18" s="14">
+        <v>12</v>
+      </c>
+      <c r="H18" s="15">
         <v>-75</v>
       </c>
-      <c r="F18" s="14">
-        <v>2</v>
-      </c>
-      <c r="G18" s="14">
-        <v>13</v>
-      </c>
-      <c r="H18" s="15">
-        <v>-84.615384615384</v>
-      </c>
       <c r="I18" s="14">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J18" s="14">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="K18" s="15">
-        <v>-70.588235294117</v>
+        <v>-68.421052631578</v>
       </c>
       <c r="L18" s="15">
-        <v>-37.5</v>
+        <v>-45.454545454545</v>
       </c>
       <c r="M18" s="13" t="s">
         <v>21</v>
@@ -1070,34 +1070,34 @@
         <v>26</v>
       </c>
       <c r="C19" s="14">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="D19" s="14">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E19" s="15">
-        <v>-16.666666666666</v>
+        <v>28.571428571428</v>
       </c>
       <c r="F19" s="14">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="G19" s="14">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="H19" s="15">
-        <v>16.666666666666</v>
+        <v>9.523809523809</v>
       </c>
       <c r="I19" s="14">
-        <v>39</v>
+        <v>48</v>
       </c>
       <c r="J19" s="14">
-        <v>43</v>
+        <v>50</v>
       </c>
       <c r="K19" s="15">
-        <v>-9.302325581395</v>
+        <v>-4</v>
       </c>
       <c r="L19" s="15">
-        <v>-18.75</v>
+        <v>-12.727272727272</v>
       </c>
       <c r="M19" s="13" t="s">
         <v>21</v>
@@ -1110,32 +1110,32 @@
       <c r="A20" s="13" t="s">
         <v>27</v>
       </c>
-      <c r="C20" s="14">
-        <v>2</v>
+      <c r="C20" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D20" s="14">
         <v>2</v>
       </c>
       <c r="E20" s="15">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="F20" s="14">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G20" s="14">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="H20" s="15">
-        <v>-66.666666666666</v>
+        <v>-80</v>
       </c>
       <c r="I20" s="14">
         <v>8</v>
       </c>
       <c r="J20" s="14">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="K20" s="15">
-        <v>-50</v>
+        <v>-55.555555555555</v>
       </c>
       <c r="L20" s="15">
         <v>166.666666666667</v>
@@ -1155,31 +1155,31 @@
         <v>12</v>
       </c>
       <c r="D21" s="17">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="E21" s="18">
-        <v>-45.454545454545</v>
+        <v>-25</v>
       </c>
       <c r="F21" s="17">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="G21" s="17">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="H21" s="18">
+        <v>-22.058823529411</v>
+      </c>
+      <c r="I21" s="17">
+        <v>110</v>
+      </c>
+      <c r="J21" s="17">
+        <v>128</v>
+      </c>
+      <c r="K21" s="18">
         <v>-14.0625</v>
       </c>
-      <c r="I21" s="17">
-        <v>97</v>
-      </c>
-      <c r="J21" s="17">
-        <v>112</v>
-      </c>
-      <c r="K21" s="18">
-        <v>-13.392857142857</v>
-      </c>
       <c r="L21" s="18">
-        <v>11.494252873563</v>
+        <v>6.796116504854</v>
       </c>
       <c r="M21" s="19" t="s">
         <v>21</v>
@@ -1233,35 +1233,35 @@
       <c r="A23" s="13" t="s">
         <v>30</v>
       </c>
-      <c r="C23" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="D23" s="14">
+      <c r="C23" s="14">
         <v>1</v>
       </c>
-      <c r="E23" s="15">
-        <v>-100</v>
-      </c>
-      <c r="F23" s="13" t="s">
-        <v>20</v>
+      <c r="D23" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E23" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="F23" s="14">
+        <v>1</v>
       </c>
       <c r="G23" s="14">
         <v>2</v>
       </c>
       <c r="H23" s="15">
-        <v>-100</v>
-      </c>
-      <c r="I23" s="13" t="s">
-        <v>20</v>
+        <v>-50</v>
+      </c>
+      <c r="I23" s="14">
+        <v>1</v>
       </c>
       <c r="J23" s="14">
         <v>2</v>
       </c>
       <c r="K23" s="15">
-        <v>-100</v>
+        <v>-50</v>
       </c>
       <c r="L23" s="15">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="M23" s="13" t="s">
         <v>21</v>
@@ -1275,34 +1275,34 @@
         <v>31</v>
       </c>
       <c r="C24" s="14">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="D24" s="14">
-        <v>35</v>
+        <v>23</v>
       </c>
       <c r="E24" s="15">
-        <v>-42.857142857142</v>
+        <v>-4.347826086956</v>
       </c>
       <c r="F24" s="14">
-        <v>73</v>
+        <v>79</v>
       </c>
       <c r="G24" s="14">
-        <v>132</v>
+        <v>120</v>
       </c>
       <c r="H24" s="15">
-        <v>-44.696969696969</v>
+        <v>-34.166666666666</v>
       </c>
       <c r="I24" s="14">
-        <v>127</v>
+        <v>149</v>
       </c>
       <c r="J24" s="14">
-        <v>203</v>
+        <v>226</v>
       </c>
       <c r="K24" s="15">
-        <v>-37.438423645320</v>
+        <v>-34.070796460177</v>
       </c>
       <c r="L24" s="15">
-        <v>-38.349514563106</v>
+        <v>-36.051502145922</v>
       </c>
       <c r="M24" s="13" t="s">
         <v>21</v>
@@ -1316,34 +1316,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="14">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="D25" s="14">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="E25" s="15">
-        <v>-55.555555555555</v>
+        <v>-6.25</v>
       </c>
       <c r="F25" s="14">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="G25" s="14">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="H25" s="15">
-        <v>-43.010752688172</v>
+        <v>-32.5</v>
       </c>
       <c r="I25" s="14">
-        <v>95</v>
+        <v>110</v>
       </c>
       <c r="J25" s="14">
-        <v>140</v>
+        <v>156</v>
       </c>
       <c r="K25" s="15">
-        <v>-32.142857142857</v>
+        <v>-29.487179487179</v>
       </c>
       <c r="L25" s="15">
-        <v>-29.629629629629</v>
+        <v>-28.571428571428</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1357,34 +1357,34 @@
         <v>33</v>
       </c>
       <c r="C26" s="14">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="D26" s="14">
         <v>6</v>
       </c>
       <c r="E26" s="15">
-        <v>66.666666666666</v>
+        <v>150</v>
       </c>
       <c r="F26" s="14">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="G26" s="14">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="H26" s="15">
-        <v>28.571428571428</v>
+        <v>62.962962962963</v>
       </c>
       <c r="I26" s="14">
-        <v>60</v>
+        <v>74</v>
       </c>
       <c r="J26" s="14">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="K26" s="15">
-        <v>20</v>
+        <v>32.142857142857</v>
       </c>
       <c r="L26" s="15">
-        <v>-1.639344262295</v>
+        <v>-3.896103896103</v>
       </c>
       <c r="M26" s="13" t="s">
         <v>21</v>
@@ -1397,8 +1397,8 @@
       <c r="A27" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="C27" s="14">
-        <v>2</v>
+      <c r="C27" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D27" s="13" t="s">
         <v>20</v>
@@ -1410,10 +1410,10 @@
         <v>4</v>
       </c>
       <c r="G27" s="14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H27" s="15">
-        <v>100</v>
+        <v>300</v>
       </c>
       <c r="I27" s="14">
         <v>6</v>
@@ -1425,7 +1425,7 @@
         <v>100</v>
       </c>
       <c r="L27" s="15">
-        <v>500</v>
+        <v>200</v>
       </c>
       <c r="M27" s="13" t="s">
         <v>21</v>
@@ -1439,34 +1439,34 @@
         <v>35</v>
       </c>
       <c r="C28" s="14">
+        <v>5</v>
+      </c>
+      <c r="D28" s="14">
         <v>1</v>
       </c>
-      <c r="D28" s="14">
-        <v>2</v>
-      </c>
       <c r="E28" s="15">
-        <v>-50</v>
+        <v>400</v>
       </c>
       <c r="F28" s="14">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="G28" s="14">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H28" s="15">
-        <v>-66.666666666666</v>
+        <v>20</v>
       </c>
       <c r="I28" s="14">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="J28" s="14">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K28" s="15">
-        <v>-22.222222222222</v>
+        <v>10</v>
       </c>
       <c r="L28" s="15">
-        <v>40</v>
+        <v>83.333333333333</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>

--- a/data/source/weekly/cs-en-us-121pct.xlsx
+++ b/data/source/weekly/cs-en-us-121pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">8</t>
+      <t xml:space="preserve">9</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">2/16/2026</t>
+      <t xml:space="preserve">2/23/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">2/22/2026</t>
+      <t xml:space="preserve">3/1/2026</t>
     </r>
   </si>
   <si>
@@ -908,29 +908,29 @@
       <c r="C15" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D15" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E15" s="13" t="s">
-        <v>21</v>
+      <c r="D15" s="14">
+        <v>1</v>
+      </c>
+      <c r="E15" s="15">
+        <v>-100</v>
       </c>
       <c r="F15" s="14">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G15" s="14">
         <v>1</v>
       </c>
       <c r="H15" s="15">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="I15" s="14">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J15" s="14">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K15" s="15">
-        <v>66.666666666666</v>
+        <v>50</v>
       </c>
       <c r="L15" s="13" t="s">
         <v>21</v>
@@ -955,26 +955,26 @@
       <c r="E16" s="15">
         <v>-100</v>
       </c>
-      <c r="F16" s="14">
-        <v>1</v>
+      <c r="F16" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="G16" s="14">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="H16" s="15">
-        <v>-75</v>
+        <v>-100</v>
       </c>
       <c r="I16" s="14">
         <v>8</v>
       </c>
       <c r="J16" s="14">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="K16" s="15">
-        <v>0</v>
+        <v>-20</v>
       </c>
       <c r="L16" s="15">
-        <v>-20</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="M16" s="13" t="s">
         <v>21</v>
@@ -988,34 +988,34 @@
         <v>24</v>
       </c>
       <c r="C17" s="14">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D17" s="14">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E17" s="15">
-        <v>-33.333333333333</v>
+        <v>50</v>
       </c>
       <c r="F17" s="14">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="G17" s="14">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="H17" s="15">
-        <v>5</v>
+        <v>11.111111111111</v>
       </c>
       <c r="I17" s="14">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="J17" s="14">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="K17" s="15">
-        <v>16.666666666666</v>
+        <v>17.647058823529</v>
       </c>
       <c r="L17" s="15">
-        <v>45.833333333333</v>
+        <v>33.333333333333</v>
       </c>
       <c r="M17" s="13" t="s">
         <v>21</v>
@@ -1032,31 +1032,31 @@
         <v>1</v>
       </c>
       <c r="D18" s="14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E18" s="15">
-        <v>-50</v>
+        <v>0</v>
       </c>
       <c r="F18" s="14">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G18" s="14">
         <v>12</v>
       </c>
       <c r="H18" s="15">
-        <v>-75</v>
+        <v>-66.666666666666</v>
       </c>
       <c r="I18" s="14">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J18" s="14">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K18" s="15">
-        <v>-68.421052631578</v>
+        <v>-65</v>
       </c>
       <c r="L18" s="15">
-        <v>-45.454545454545</v>
+        <v>-41.666666666666</v>
       </c>
       <c r="M18" s="13" t="s">
         <v>21</v>
@@ -1070,34 +1070,34 @@
         <v>26</v>
       </c>
       <c r="C19" s="14">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="D19" s="14">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="E19" s="15">
-        <v>28.571428571428</v>
+        <v>-71.428571428571</v>
       </c>
       <c r="F19" s="14">
         <v>23</v>
       </c>
       <c r="G19" s="14">
-        <v>21</v>
+        <v>31</v>
       </c>
       <c r="H19" s="15">
-        <v>9.523809523809</v>
+        <v>-25.806451612903</v>
       </c>
       <c r="I19" s="14">
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="J19" s="14">
-        <v>50</v>
+        <v>64</v>
       </c>
       <c r="K19" s="15">
-        <v>-4</v>
+        <v>-17.1875</v>
       </c>
       <c r="L19" s="15">
-        <v>-12.727272727272</v>
+        <v>-10.169491525423</v>
       </c>
       <c r="M19" s="13" t="s">
         <v>21</v>
@@ -1114,7 +1114,7 @@
         <v>20</v>
       </c>
       <c r="D20" s="14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E20" s="15">
         <v>-100</v>
@@ -1123,19 +1123,19 @@
         <v>2</v>
       </c>
       <c r="G20" s="14">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="H20" s="15">
-        <v>-80</v>
+        <v>-71.428571428571</v>
       </c>
       <c r="I20" s="14">
         <v>8</v>
       </c>
       <c r="J20" s="14">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="K20" s="15">
-        <v>-55.555555555555</v>
+        <v>-57.894736842105</v>
       </c>
       <c r="L20" s="15">
         <v>166.666666666667</v>
@@ -1152,34 +1152,34 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D21" s="17">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="E21" s="18">
-        <v>-25</v>
+        <v>-52.173913043478</v>
       </c>
       <c r="F21" s="17">
         <v>53</v>
       </c>
       <c r="G21" s="17">
-        <v>68</v>
+        <v>75</v>
       </c>
       <c r="H21" s="18">
-        <v>-22.058823529411</v>
+        <v>-29.333333333333</v>
       </c>
       <c r="I21" s="17">
-        <v>110</v>
+        <v>122</v>
       </c>
       <c r="J21" s="17">
-        <v>128</v>
+        <v>151</v>
       </c>
       <c r="K21" s="18">
-        <v>-14.0625</v>
+        <v>-19.205298013245</v>
       </c>
       <c r="L21" s="18">
-        <v>6.796116504854</v>
+        <v>5.172413793103</v>
       </c>
       <c r="M21" s="19" t="s">
         <v>21</v>
@@ -1233,8 +1233,8 @@
       <c r="A23" s="13" t="s">
         <v>30</v>
       </c>
-      <c r="C23" s="14">
-        <v>1</v>
+      <c r="C23" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D23" s="13" t="s">
         <v>20</v>
@@ -1275,34 +1275,34 @@
         <v>31</v>
       </c>
       <c r="C24" s="14">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="D24" s="14">
-        <v>23</v>
+        <v>33</v>
       </c>
       <c r="E24" s="15">
-        <v>-4.347826086956</v>
+        <v>-60.606060606060</v>
       </c>
       <c r="F24" s="14">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="G24" s="14">
-        <v>120</v>
+        <v>128</v>
       </c>
       <c r="H24" s="15">
-        <v>-34.166666666666</v>
+        <v>-39.84375</v>
       </c>
       <c r="I24" s="14">
-        <v>149</v>
+        <v>162</v>
       </c>
       <c r="J24" s="14">
-        <v>226</v>
+        <v>259</v>
       </c>
       <c r="K24" s="15">
-        <v>-34.070796460177</v>
+        <v>-37.451737451737</v>
       </c>
       <c r="L24" s="15">
-        <v>-36.051502145922</v>
+        <v>-40.221402214022</v>
       </c>
       <c r="M24" s="13" t="s">
         <v>21</v>
@@ -1316,34 +1316,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="14">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="D25" s="14">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="E25" s="15">
-        <v>-6.25</v>
+        <v>-47.619047619047</v>
       </c>
       <c r="F25" s="14">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="G25" s="14">
-        <v>80</v>
+        <v>86</v>
       </c>
       <c r="H25" s="15">
-        <v>-32.5</v>
+        <v>-39.534883720930</v>
       </c>
       <c r="I25" s="14">
-        <v>110</v>
+        <v>121</v>
       </c>
       <c r="J25" s="14">
-        <v>156</v>
+        <v>177</v>
       </c>
       <c r="K25" s="15">
-        <v>-29.487179487179</v>
+        <v>-31.638418079096</v>
       </c>
       <c r="L25" s="15">
-        <v>-28.571428571428</v>
+        <v>-34.946236559139</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1357,34 +1357,34 @@
         <v>33</v>
       </c>
       <c r="C26" s="14">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D26" s="14">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="E26" s="15">
-        <v>150</v>
+        <v>33.333333333333</v>
       </c>
       <c r="F26" s="14">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="G26" s="14">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="H26" s="15">
-        <v>62.962962962963</v>
+        <v>62.5</v>
       </c>
       <c r="I26" s="14">
-        <v>74</v>
+        <v>92</v>
       </c>
       <c r="J26" s="14">
-        <v>56</v>
+        <v>68</v>
       </c>
       <c r="K26" s="15">
-        <v>32.142857142857</v>
+        <v>35.294117647058</v>
       </c>
       <c r="L26" s="15">
-        <v>-3.896103896103</v>
+        <v>0</v>
       </c>
       <c r="M26" s="13" t="s">
         <v>21</v>
@@ -1400,32 +1400,32 @@
       <c r="C27" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D27" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E27" s="13" t="s">
-        <v>21</v>
+      <c r="D27" s="14">
+        <v>1</v>
+      </c>
+      <c r="E27" s="15">
+        <v>-100</v>
       </c>
       <c r="F27" s="14">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G27" s="14">
         <v>1</v>
       </c>
       <c r="H27" s="15">
-        <v>300</v>
+        <v>400</v>
       </c>
       <c r="I27" s="14">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J27" s="14">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K27" s="15">
-        <v>100</v>
+        <v>75</v>
       </c>
       <c r="L27" s="15">
-        <v>200</v>
+        <v>250</v>
       </c>
       <c r="M27" s="13" t="s">
         <v>21</v>
@@ -1439,34 +1439,34 @@
         <v>35</v>
       </c>
       <c r="C28" s="14">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D28" s="14">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E28" s="15">
-        <v>400</v>
+        <v>-25</v>
       </c>
       <c r="F28" s="14">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="G28" s="14">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="H28" s="15">
-        <v>20</v>
+        <v>-11.111111111111</v>
       </c>
       <c r="I28" s="14">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="J28" s="14">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="K28" s="15">
-        <v>10</v>
+        <v>-7.142857142857</v>
       </c>
       <c r="L28" s="15">
-        <v>83.333333333333</v>
+        <v>62.5</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>

--- a/data/source/weekly/cs-en-us-121pct.xlsx
+++ b/data/source/weekly/cs-en-us-121pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">9</t>
+      <t xml:space="preserve">10</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">2/23/2026</t>
+      <t xml:space="preserve">3/2/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/1/2026</t>
+      <t xml:space="preserve">3/8/2026</t>
     </r>
   </si>
   <si>
@@ -705,7 +705,7 @@
     <col min="2" max="2" width="12.495057" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="6.168446" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="7.433768" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="7.433768" bestFit="1" customWidth="1"/>
@@ -908,20 +908,20 @@
       <c r="C15" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D15" s="14">
-        <v>1</v>
-      </c>
-      <c r="E15" s="15">
-        <v>-100</v>
+      <c r="D15" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E15" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F15" s="14">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G15" s="14">
         <v>1</v>
       </c>
       <c r="H15" s="15">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="I15" s="14">
         <v>6</v>
@@ -946,35 +946,35 @@
       <c r="A16" s="13" t="s">
         <v>23</v>
       </c>
-      <c r="C16" s="13" t="s">
-        <v>20</v>
+      <c r="C16" s="14">
+        <v>1</v>
       </c>
       <c r="D16" s="14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E16" s="15">
-        <v>-100</v>
-      </c>
-      <c r="F16" s="13" t="s">
-        <v>20</v>
+        <v>0</v>
+      </c>
+      <c r="F16" s="14">
+        <v>1</v>
       </c>
       <c r="G16" s="14">
         <v>6</v>
       </c>
       <c r="H16" s="15">
-        <v>-100</v>
+        <v>-83.333333333333</v>
       </c>
       <c r="I16" s="14">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J16" s="14">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="K16" s="15">
-        <v>-20</v>
+        <v>-18.181818181818</v>
       </c>
       <c r="L16" s="15">
-        <v>-33.333333333333</v>
+        <v>-30.769230769230</v>
       </c>
       <c r="M16" s="13" t="s">
         <v>21</v>
@@ -988,34 +988,34 @@
         <v>24</v>
       </c>
       <c r="C17" s="14">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D17" s="14">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E17" s="15">
-        <v>50</v>
+        <v>33.333333333333</v>
       </c>
       <c r="F17" s="14">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="G17" s="14">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="H17" s="15">
-        <v>11.111111111111</v>
+        <v>-6.666666666666</v>
       </c>
       <c r="I17" s="14">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="J17" s="14">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="K17" s="15">
-        <v>17.647058823529</v>
+        <v>21.621621621621</v>
       </c>
       <c r="L17" s="15">
-        <v>33.333333333333</v>
+        <v>28.571428571428</v>
       </c>
       <c r="M17" s="13" t="s">
         <v>21</v>
@@ -1032,31 +1032,31 @@
         <v>1</v>
       </c>
       <c r="D18" s="14">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E18" s="15">
-        <v>0</v>
+        <v>-66.666666666666</v>
       </c>
       <c r="F18" s="14">
         <v>4</v>
       </c>
       <c r="G18" s="14">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="H18" s="15">
-        <v>-66.666666666666</v>
+        <v>-71.428571428571</v>
       </c>
       <c r="I18" s="14">
         <v>7</v>
       </c>
       <c r="J18" s="14">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="K18" s="15">
-        <v>-65</v>
+        <v>-69.565217391304</v>
       </c>
       <c r="L18" s="15">
-        <v>-41.666666666666</v>
+        <v>-46.153846153846</v>
       </c>
       <c r="M18" s="13" t="s">
         <v>21</v>
@@ -1070,34 +1070,34 @@
         <v>26</v>
       </c>
       <c r="C19" s="14">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="D19" s="14">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="E19" s="15">
-        <v>-71.428571428571</v>
+        <v>28.571428571428</v>
       </c>
       <c r="F19" s="14">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="G19" s="14">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="H19" s="15">
-        <v>-25.806451612903</v>
+        <v>-17.647058823529</v>
       </c>
       <c r="I19" s="14">
-        <v>53</v>
+        <v>62</v>
       </c>
       <c r="J19" s="14">
-        <v>64</v>
+        <v>71</v>
       </c>
       <c r="K19" s="15">
-        <v>-17.1875</v>
+        <v>-12.676056338028</v>
       </c>
       <c r="L19" s="15">
-        <v>-10.169491525423</v>
+        <v>-10.144927536231</v>
       </c>
       <c r="M19" s="13" t="s">
         <v>21</v>
@@ -1113,20 +1113,20 @@
       <c r="C20" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D20" s="14">
-        <v>1</v>
-      </c>
-      <c r="E20" s="15">
-        <v>-100</v>
+      <c r="D20" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E20" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F20" s="14">
         <v>2</v>
       </c>
       <c r="G20" s="14">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="H20" s="15">
-        <v>-71.428571428571</v>
+        <v>-60</v>
       </c>
       <c r="I20" s="14">
         <v>8</v>
@@ -1138,7 +1138,7 @@
         <v>-57.894736842105</v>
       </c>
       <c r="L20" s="15">
-        <v>166.666666666667</v>
+        <v>100</v>
       </c>
       <c r="M20" s="13" t="s">
         <v>21</v>
@@ -1152,34 +1152,34 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="D21" s="17">
-        <v>23</v>
+        <v>14</v>
       </c>
       <c r="E21" s="18">
-        <v>-52.173913043478</v>
+        <v>7.142857142857</v>
       </c>
       <c r="F21" s="17">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="G21" s="17">
         <v>75</v>
       </c>
       <c r="H21" s="18">
-        <v>-29.333333333333</v>
+        <v>-30.666666666666</v>
       </c>
       <c r="I21" s="17">
-        <v>122</v>
+        <v>137</v>
       </c>
       <c r="J21" s="17">
-        <v>151</v>
+        <v>165</v>
       </c>
       <c r="K21" s="18">
-        <v>-19.205298013245</v>
+        <v>-16.969696969697</v>
       </c>
       <c r="L21" s="18">
-        <v>5.172413793103</v>
+        <v>2.238805970149</v>
       </c>
       <c r="M21" s="19" t="s">
         <v>21</v>
@@ -1246,10 +1246,10 @@
         <v>1</v>
       </c>
       <c r="G23" s="14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H23" s="15">
-        <v>-50</v>
+        <v>0</v>
       </c>
       <c r="I23" s="14">
         <v>1</v>
@@ -1275,34 +1275,34 @@
         <v>31</v>
       </c>
       <c r="C24" s="14">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="D24" s="14">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="E24" s="15">
-        <v>-60.606060606060</v>
+        <v>-22.222222222222</v>
       </c>
       <c r="F24" s="14">
         <v>77</v>
       </c>
       <c r="G24" s="14">
-        <v>128</v>
+        <v>118</v>
       </c>
       <c r="H24" s="15">
-        <v>-39.84375</v>
+        <v>-34.745762711864</v>
       </c>
       <c r="I24" s="14">
-        <v>162</v>
+        <v>184</v>
       </c>
       <c r="J24" s="14">
-        <v>259</v>
+        <v>286</v>
       </c>
       <c r="K24" s="15">
-        <v>-37.451737451737</v>
+        <v>-35.664335664335</v>
       </c>
       <c r="L24" s="15">
-        <v>-40.221402214022</v>
+        <v>-38.666666666666</v>
       </c>
       <c r="M24" s="13" t="s">
         <v>21</v>
@@ -1319,31 +1319,31 @@
         <v>11</v>
       </c>
       <c r="D25" s="14">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="E25" s="15">
-        <v>-47.619047619047</v>
+        <v>-35.294117647058</v>
       </c>
       <c r="F25" s="14">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="G25" s="14">
-        <v>86</v>
+        <v>81</v>
       </c>
       <c r="H25" s="15">
-        <v>-39.534883720930</v>
+        <v>-39.506172839506</v>
       </c>
       <c r="I25" s="14">
-        <v>121</v>
+        <v>132</v>
       </c>
       <c r="J25" s="14">
-        <v>177</v>
+        <v>194</v>
       </c>
       <c r="K25" s="15">
-        <v>-31.638418079096</v>
+        <v>-31.958762886597</v>
       </c>
       <c r="L25" s="15">
-        <v>-34.946236559139</v>
+        <v>-36.538461538461</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1357,34 +1357,34 @@
         <v>33</v>
       </c>
       <c r="C26" s="14">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="D26" s="14">
         <v>12</v>
       </c>
       <c r="E26" s="15">
-        <v>33.333333333333</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="F26" s="14">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="G26" s="14">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="H26" s="15">
-        <v>62.5</v>
+        <v>38.888888888888</v>
       </c>
       <c r="I26" s="14">
-        <v>92</v>
+        <v>100</v>
       </c>
       <c r="J26" s="14">
-        <v>68</v>
+        <v>80</v>
       </c>
       <c r="K26" s="15">
-        <v>35.294117647058</v>
+        <v>25</v>
       </c>
       <c r="L26" s="15">
-        <v>0</v>
+        <v>-4.761904761904</v>
       </c>
       <c r="M26" s="13" t="s">
         <v>21</v>
@@ -1400,20 +1400,20 @@
       <c r="C27" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D27" s="14">
-        <v>1</v>
-      </c>
-      <c r="E27" s="15">
-        <v>-100</v>
+      <c r="D27" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E27" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F27" s="14">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G27" s="14">
         <v>1</v>
       </c>
       <c r="H27" s="15">
-        <v>400</v>
+        <v>200</v>
       </c>
       <c r="I27" s="14">
         <v>7</v>
@@ -1438,23 +1438,23 @@
       <c r="A28" s="13" t="s">
         <v>35</v>
       </c>
-      <c r="C28" s="14">
-        <v>3</v>
-      </c>
-      <c r="D28" s="14">
-        <v>4</v>
-      </c>
-      <c r="E28" s="15">
-        <v>-25</v>
+      <c r="C28" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D28" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E28" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F28" s="14">
         <v>8</v>
       </c>
       <c r="G28" s="14">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="H28" s="15">
-        <v>-11.111111111111</v>
+        <v>14.285714285714</v>
       </c>
       <c r="I28" s="14">
         <v>13</v>
@@ -1479,8 +1479,8 @@
       <c r="A29" s="13" t="s">
         <v>36</v>
       </c>
-      <c r="C29" s="13" t="s">
-        <v>20</v>
+      <c r="C29" s="14">
+        <v>1</v>
       </c>
       <c r="D29" s="13" t="s">
         <v>20</v>
@@ -1488,8 +1488,8 @@
       <c r="E29" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="F29" s="13" t="s">
-        <v>20</v>
+      <c r="F29" s="14">
+        <v>1</v>
       </c>
       <c r="G29" s="13" t="s">
         <v>20</v>
@@ -1497,8 +1497,8 @@
       <c r="H29" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="I29" s="13" t="s">
-        <v>20</v>
+      <c r="I29" s="14">
+        <v>1</v>
       </c>
       <c r="J29" s="13" t="s">
         <v>20</v>
@@ -1520,8 +1520,8 @@
       <c r="A30" s="13" t="s">
         <v>37</v>
       </c>
-      <c r="C30" s="13" t="s">
-        <v>20</v>
+      <c r="C30" s="14">
+        <v>1</v>
       </c>
       <c r="D30" s="13" t="s">
         <v>20</v>
@@ -1529,8 +1529,8 @@
       <c r="E30" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="F30" s="13" t="s">
-        <v>20</v>
+      <c r="F30" s="14">
+        <v>1</v>
       </c>
       <c r="G30" s="13" t="s">
         <v>20</v>
@@ -1538,8 +1538,8 @@
       <c r="H30" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="I30" s="13" t="s">
-        <v>20</v>
+      <c r="I30" s="14">
+        <v>1</v>
       </c>
       <c r="J30" s="13" t="s">
         <v>20</v>
@@ -1561,8 +1561,8 @@
       <c r="A31" s="13" t="s">
         <v>38</v>
       </c>
-      <c r="C31" s="13" t="s">
-        <v>20</v>
+      <c r="C31" s="14">
+        <v>1</v>
       </c>
       <c r="D31" s="13" t="s">
         <v>20</v>
@@ -1570,8 +1570,8 @@
       <c r="E31" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="F31" s="13" t="s">
-        <v>20</v>
+      <c r="F31" s="14">
+        <v>1</v>
       </c>
       <c r="G31" s="13" t="s">
         <v>20</v>
@@ -1579,8 +1579,8 @@
       <c r="H31" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="I31" s="13" t="s">
-        <v>20</v>
+      <c r="I31" s="14">
+        <v>1</v>
       </c>
       <c r="J31" s="13" t="s">
         <v>20</v>
@@ -1589,7 +1589,7 @@
         <v>21</v>
       </c>
       <c r="L31" s="15">
-        <v>-100</v>
+        <v>-66.666666666666</v>
       </c>
       <c r="M31" s="13" t="s">
         <v>21</v>

--- a/data/source/weekly/cs-en-us-121pct.xlsx
+++ b/data/source/weekly/cs-en-us-121pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">10</t>
+      <t xml:space="preserve">11</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/2/2026</t>
+      <t xml:space="preserve">3/9/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/8/2026</t>
+      <t xml:space="preserve">3/15/2026</t>
     </r>
   </si>
   <si>
@@ -914,14 +914,14 @@
       <c r="E15" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="F15" s="14">
-        <v>3</v>
+      <c r="F15" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="G15" s="14">
         <v>1</v>
       </c>
       <c r="H15" s="15">
-        <v>200</v>
+        <v>-100</v>
       </c>
       <c r="I15" s="14">
         <v>6</v>
@@ -947,34 +947,34 @@
         <v>23</v>
       </c>
       <c r="C16" s="14">
-        <v>1</v>
-      </c>
-      <c r="D16" s="14">
-        <v>1</v>
-      </c>
-      <c r="E16" s="15">
-        <v>0</v>
+        <v>2</v>
+      </c>
+      <c r="D16" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E16" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F16" s="14">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G16" s="14">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H16" s="15">
-        <v>-83.333333333333</v>
+        <v>-40</v>
       </c>
       <c r="I16" s="14">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="J16" s="14">
         <v>11</v>
       </c>
       <c r="K16" s="15">
-        <v>-18.181818181818</v>
+        <v>0</v>
       </c>
       <c r="L16" s="15">
-        <v>-30.769230769230</v>
+        <v>-15.384615384615</v>
       </c>
       <c r="M16" s="13" t="s">
         <v>21</v>
@@ -988,34 +988,34 @@
         <v>24</v>
       </c>
       <c r="C17" s="14">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="D17" s="14">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E17" s="15">
-        <v>33.333333333333</v>
+        <v>350</v>
       </c>
       <c r="F17" s="14">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="G17" s="14">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="H17" s="15">
-        <v>-6.666666666666</v>
+        <v>75</v>
       </c>
       <c r="I17" s="14">
-        <v>45</v>
+        <v>54</v>
       </c>
       <c r="J17" s="14">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="K17" s="15">
-        <v>21.621621621621</v>
+        <v>38.461538461538</v>
       </c>
       <c r="L17" s="15">
-        <v>28.571428571428</v>
+        <v>38.461538461538</v>
       </c>
       <c r="M17" s="13" t="s">
         <v>21</v>
@@ -1029,34 +1029,34 @@
         <v>25</v>
       </c>
       <c r="C18" s="14">
-        <v>1</v>
-      </c>
-      <c r="D18" s="14">
-        <v>3</v>
-      </c>
-      <c r="E18" s="15">
-        <v>-66.666666666666</v>
+        <v>2</v>
+      </c>
+      <c r="D18" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E18" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F18" s="14">
         <v>4</v>
       </c>
       <c r="G18" s="14">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="H18" s="15">
-        <v>-71.428571428571</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="I18" s="14">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="J18" s="14">
         <v>23</v>
       </c>
       <c r="K18" s="15">
-        <v>-69.565217391304</v>
+        <v>-60.869565217391</v>
       </c>
       <c r="L18" s="15">
-        <v>-46.153846153846</v>
+        <v>-30.769230769230</v>
       </c>
       <c r="M18" s="13" t="s">
         <v>21</v>
@@ -1070,34 +1070,34 @@
         <v>26</v>
       </c>
       <c r="C19" s="14">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="D19" s="14">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E19" s="15">
-        <v>28.571428571428</v>
+        <v>-40</v>
       </c>
       <c r="F19" s="14">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G19" s="14">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="H19" s="15">
-        <v>-17.647058823529</v>
+        <v>-28.947368421052</v>
       </c>
       <c r="I19" s="14">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="J19" s="14">
-        <v>71</v>
+        <v>81</v>
       </c>
       <c r="K19" s="15">
-        <v>-12.676056338028</v>
+        <v>-17.283950617283</v>
       </c>
       <c r="L19" s="15">
-        <v>-10.144927536231</v>
+        <v>-9.459459459459</v>
       </c>
       <c r="M19" s="13" t="s">
         <v>21</v>
@@ -1110,32 +1110,32 @@
       <c r="A20" s="13" t="s">
         <v>27</v>
       </c>
-      <c r="C20" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="D20" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E20" s="13" t="s">
-        <v>21</v>
+      <c r="C20" s="14">
+        <v>2</v>
+      </c>
+      <c r="D20" s="14">
+        <v>1</v>
+      </c>
+      <c r="E20" s="15">
+        <v>100</v>
       </c>
       <c r="F20" s="14">
         <v>2</v>
       </c>
       <c r="G20" s="14">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H20" s="15">
-        <v>-60</v>
+        <v>-50</v>
       </c>
       <c r="I20" s="14">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="J20" s="14">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K20" s="15">
-        <v>-57.894736842105</v>
+        <v>-50</v>
       </c>
       <c r="L20" s="15">
         <v>100</v>
@@ -1152,34 +1152,34 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="D21" s="17">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E21" s="18">
-        <v>7.142857142857</v>
+        <v>61.538461538461</v>
       </c>
       <c r="F21" s="17">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="G21" s="17">
-        <v>75</v>
+        <v>66</v>
       </c>
       <c r="H21" s="18">
-        <v>-30.666666666666</v>
+        <v>-13.636363636363</v>
       </c>
       <c r="I21" s="17">
-        <v>137</v>
+        <v>157</v>
       </c>
       <c r="J21" s="17">
-        <v>165</v>
+        <v>178</v>
       </c>
       <c r="K21" s="18">
-        <v>-16.969696969697</v>
+        <v>-11.797752808988</v>
       </c>
       <c r="L21" s="18">
-        <v>2.238805970149</v>
+        <v>9.027777777777</v>
       </c>
       <c r="M21" s="19" t="s">
         <v>21</v>
@@ -1233,8 +1233,8 @@
       <c r="A23" s="13" t="s">
         <v>30</v>
       </c>
-      <c r="C23" s="13" t="s">
-        <v>20</v>
+      <c r="C23" s="14">
+        <v>1</v>
       </c>
       <c r="D23" s="13" t="s">
         <v>20</v>
@@ -1243,25 +1243,25 @@
         <v>21</v>
       </c>
       <c r="F23" s="14">
-        <v>1</v>
-      </c>
-      <c r="G23" s="14">
-        <v>1</v>
-      </c>
-      <c r="H23" s="15">
-        <v>0</v>
+        <v>2</v>
+      </c>
+      <c r="G23" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="H23" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="I23" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J23" s="14">
         <v>2</v>
       </c>
       <c r="K23" s="15">
-        <v>-50</v>
+        <v>0</v>
       </c>
       <c r="L23" s="15">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M23" s="13" t="s">
         <v>21</v>
@@ -1278,31 +1278,31 @@
         <v>21</v>
       </c>
       <c r="D24" s="14">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="E24" s="15">
-        <v>-22.222222222222</v>
+        <v>0</v>
       </c>
       <c r="F24" s="14">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="G24" s="14">
-        <v>118</v>
+        <v>104</v>
       </c>
       <c r="H24" s="15">
-        <v>-34.745762711864</v>
+        <v>-24.038461538461</v>
       </c>
       <c r="I24" s="14">
-        <v>184</v>
+        <v>206</v>
       </c>
       <c r="J24" s="14">
-        <v>286</v>
+        <v>307</v>
       </c>
       <c r="K24" s="15">
-        <v>-35.664335664335</v>
+        <v>-32.899022801302</v>
       </c>
       <c r="L24" s="15">
-        <v>-38.666666666666</v>
+        <v>-38.872403560830</v>
       </c>
       <c r="M24" s="13" t="s">
         <v>21</v>
@@ -1316,34 +1316,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="14">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="D25" s="14">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="E25" s="15">
-        <v>-35.294117647058</v>
+        <v>0</v>
       </c>
       <c r="F25" s="14">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="G25" s="14">
-        <v>81</v>
+        <v>67</v>
       </c>
       <c r="H25" s="15">
-        <v>-39.506172839506</v>
+        <v>-23.880597014925</v>
       </c>
       <c r="I25" s="14">
-        <v>132</v>
+        <v>146</v>
       </c>
       <c r="J25" s="14">
-        <v>194</v>
+        <v>207</v>
       </c>
       <c r="K25" s="15">
-        <v>-31.958762886597</v>
+        <v>-29.468599033816</v>
       </c>
       <c r="L25" s="15">
-        <v>-36.538461538461</v>
+        <v>-38.655462184873</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1357,34 +1357,34 @@
         <v>33</v>
       </c>
       <c r="C26" s="14">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D26" s="14">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="E26" s="15">
-        <v>-33.333333333333</v>
+        <v>-58.823529411764</v>
       </c>
       <c r="F26" s="14">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G26" s="14">
-        <v>36</v>
+        <v>47</v>
       </c>
       <c r="H26" s="15">
-        <v>38.888888888888</v>
+        <v>4.255319148936</v>
       </c>
       <c r="I26" s="14">
-        <v>100</v>
+        <v>108</v>
       </c>
       <c r="J26" s="14">
-        <v>80</v>
+        <v>97</v>
       </c>
       <c r="K26" s="15">
-        <v>25</v>
+        <v>11.340206185567</v>
       </c>
       <c r="L26" s="15">
-        <v>-4.761904761904</v>
+        <v>-10</v>
       </c>
       <c r="M26" s="13" t="s">
         <v>21</v>
@@ -1397,8 +1397,8 @@
       <c r="A27" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="C27" s="13" t="s">
-        <v>20</v>
+      <c r="C27" s="14">
+        <v>1</v>
       </c>
       <c r="D27" s="13" t="s">
         <v>20</v>
@@ -1407,25 +1407,25 @@
         <v>21</v>
       </c>
       <c r="F27" s="14">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G27" s="14">
         <v>1</v>
       </c>
       <c r="H27" s="15">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="I27" s="14">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J27" s="14">
         <v>4</v>
       </c>
       <c r="K27" s="15">
-        <v>75</v>
+        <v>100</v>
       </c>
       <c r="L27" s="15">
-        <v>250</v>
+        <v>300</v>
       </c>
       <c r="M27" s="13" t="s">
         <v>21</v>
@@ -1438,8 +1438,8 @@
       <c r="A28" s="13" t="s">
         <v>35</v>
       </c>
-      <c r="C28" s="13" t="s">
-        <v>20</v>
+      <c r="C28" s="14">
+        <v>1</v>
       </c>
       <c r="D28" s="13" t="s">
         <v>20</v>
@@ -1448,25 +1448,25 @@
         <v>21</v>
       </c>
       <c r="F28" s="14">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G28" s="14">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="H28" s="15">
-        <v>14.285714285714</v>
+        <v>80</v>
       </c>
       <c r="I28" s="14">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J28" s="14">
         <v>14</v>
       </c>
       <c r="K28" s="15">
-        <v>-7.142857142857</v>
+        <v>0</v>
       </c>
       <c r="L28" s="15">
-        <v>62.5</v>
+        <v>55.555555555555</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1479,8 +1479,8 @@
       <c r="A29" s="13" t="s">
         <v>36</v>
       </c>
-      <c r="C29" s="14">
-        <v>1</v>
+      <c r="C29" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D29" s="13" t="s">
         <v>20</v>
@@ -1520,8 +1520,8 @@
       <c r="A30" s="13" t="s">
         <v>37</v>
       </c>
-      <c r="C30" s="14">
-        <v>1</v>
+      <c r="C30" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D30" s="13" t="s">
         <v>20</v>
@@ -1561,8 +1561,8 @@
       <c r="A31" s="13" t="s">
         <v>38</v>
       </c>
-      <c r="C31" s="14">
-        <v>1</v>
+      <c r="C31" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D31" s="13" t="s">
         <v>20</v>
@@ -1647,8 +1647,8 @@
       <c r="K33" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="L33" s="13" t="s">
-        <v>21</v>
+      <c r="L33" s="15">
+        <v>50</v>
       </c>
       <c r="M33" s="13" t="s">
         <v>21</v>

--- a/data/source/weekly/cs-en-us-121pct.xlsx
+++ b/data/source/weekly/cs-en-us-121pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">11</t>
+      <t xml:space="preserve">12</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/9/2026</t>
+      <t xml:space="preserve">3/16/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/15/2026</t>
+      <t xml:space="preserve">3/22/2026</t>
     </r>
   </si>
   <si>
@@ -705,7 +705,7 @@
     <col min="2" max="2" width="12.495057" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="6.168446" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="6.168446" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="7.433768" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="7.433768" bestFit="1" customWidth="1"/>
@@ -908,17 +908,17 @@
       <c r="C15" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D15" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E15" s="13" t="s">
-        <v>21</v>
+      <c r="D15" s="14">
+        <v>4</v>
+      </c>
+      <c r="E15" s="15">
+        <v>-100</v>
       </c>
       <c r="F15" s="13" t="s">
         <v>20</v>
       </c>
       <c r="G15" s="14">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="H15" s="15">
         <v>-100</v>
@@ -927,13 +927,13 @@
         <v>6</v>
       </c>
       <c r="J15" s="14">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="K15" s="15">
-        <v>50</v>
-      </c>
-      <c r="L15" s="13" t="s">
-        <v>21</v>
+        <v>-25</v>
+      </c>
+      <c r="L15" s="15">
+        <v>200</v>
       </c>
       <c r="M15" s="13" t="s">
         <v>21</v>
@@ -956,25 +956,25 @@
         <v>21</v>
       </c>
       <c r="F16" s="14">
+        <v>5</v>
+      </c>
+      <c r="G16" s="14">
         <v>3</v>
       </c>
-      <c r="G16" s="14">
-        <v>5</v>
-      </c>
       <c r="H16" s="15">
-        <v>-40</v>
+        <v>66.666666666666</v>
       </c>
       <c r="I16" s="14">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="J16" s="14">
         <v>11</v>
       </c>
       <c r="K16" s="15">
-        <v>0</v>
+        <v>18.181818181818</v>
       </c>
       <c r="L16" s="15">
-        <v>-15.384615384615</v>
+        <v>-7.142857142857</v>
       </c>
       <c r="M16" s="13" t="s">
         <v>21</v>
@@ -988,34 +988,34 @@
         <v>24</v>
       </c>
       <c r="C17" s="14">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="D17" s="14">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E17" s="15">
-        <v>350</v>
+        <v>50</v>
       </c>
       <c r="F17" s="14">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="G17" s="14">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="H17" s="15">
-        <v>75</v>
+        <v>100</v>
       </c>
       <c r="I17" s="14">
-        <v>54</v>
+        <v>60</v>
       </c>
       <c r="J17" s="14">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="K17" s="15">
-        <v>38.461538461538</v>
+        <v>39.534883720930</v>
       </c>
       <c r="L17" s="15">
-        <v>38.461538461538</v>
+        <v>22.448979591836</v>
       </c>
       <c r="M17" s="13" t="s">
         <v>21</v>
@@ -1029,7 +1029,7 @@
         <v>25</v>
       </c>
       <c r="C18" s="14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D18" s="13" t="s">
         <v>20</v>
@@ -1041,22 +1041,22 @@
         <v>4</v>
       </c>
       <c r="G18" s="14">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="H18" s="15">
-        <v>-33.333333333333</v>
+        <v>0</v>
       </c>
       <c r="I18" s="14">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J18" s="14">
         <v>23</v>
       </c>
       <c r="K18" s="15">
-        <v>-60.869565217391</v>
+        <v>-56.521739130434</v>
       </c>
       <c r="L18" s="15">
-        <v>-30.769230769230</v>
+        <v>-23.076923076923</v>
       </c>
       <c r="M18" s="13" t="s">
         <v>21</v>
@@ -1070,34 +1070,34 @@
         <v>26</v>
       </c>
       <c r="C19" s="14">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="D19" s="14">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="E19" s="15">
-        <v>-40</v>
+        <v>125</v>
       </c>
       <c r="F19" s="14">
         <v>27</v>
       </c>
       <c r="G19" s="14">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="H19" s="15">
-        <v>-28.947368421052</v>
+        <v>-22.857142857142</v>
       </c>
       <c r="I19" s="14">
-        <v>67</v>
+        <v>76</v>
       </c>
       <c r="J19" s="14">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="K19" s="15">
-        <v>-17.283950617283</v>
+        <v>-10.588235294117</v>
       </c>
       <c r="L19" s="15">
-        <v>-9.459459459459</v>
+        <v>-7.317073170731</v>
       </c>
       <c r="M19" s="13" t="s">
         <v>21</v>
@@ -1113,29 +1113,29 @@
       <c r="C20" s="14">
         <v>2</v>
       </c>
-      <c r="D20" s="14">
-        <v>1</v>
-      </c>
-      <c r="E20" s="15">
+      <c r="D20" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E20" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="F20" s="14">
+        <v>4</v>
+      </c>
+      <c r="G20" s="14">
+        <v>2</v>
+      </c>
+      <c r="H20" s="15">
         <v>100</v>
       </c>
-      <c r="F20" s="14">
-        <v>2</v>
-      </c>
-      <c r="G20" s="14">
-        <v>4</v>
-      </c>
-      <c r="H20" s="15">
-        <v>-50</v>
-      </c>
       <c r="I20" s="14">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="J20" s="14">
         <v>20</v>
       </c>
       <c r="K20" s="15">
-        <v>-50</v>
+        <v>-40</v>
       </c>
       <c r="L20" s="15">
         <v>100</v>
@@ -1152,34 +1152,34 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D21" s="17">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E21" s="18">
-        <v>61.538461538461</v>
+        <v>66.666666666666</v>
       </c>
       <c r="F21" s="17">
-        <v>57</v>
+        <v>66</v>
       </c>
       <c r="G21" s="17">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="H21" s="18">
-        <v>-13.636363636363</v>
+        <v>6.451612903225</v>
       </c>
       <c r="I21" s="17">
-        <v>157</v>
+        <v>177</v>
       </c>
       <c r="J21" s="17">
-        <v>178</v>
+        <v>190</v>
       </c>
       <c r="K21" s="18">
-        <v>-11.797752808988</v>
+        <v>-6.842105263157</v>
       </c>
       <c r="L21" s="18">
-        <v>9.027777777777</v>
+        <v>6.626506024096</v>
       </c>
       <c r="M21" s="19" t="s">
         <v>21</v>
@@ -1233,32 +1233,32 @@
       <c r="A23" s="13" t="s">
         <v>30</v>
       </c>
-      <c r="C23" s="14">
+      <c r="C23" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D23" s="14">
         <v>1</v>
       </c>
-      <c r="D23" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E23" s="13" t="s">
-        <v>21</v>
+      <c r="E23" s="15">
+        <v>-100</v>
       </c>
       <c r="F23" s="14">
-        <v>2</v>
-      </c>
-      <c r="G23" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="H23" s="13" t="s">
-        <v>21</v>
+        <v>1</v>
+      </c>
+      <c r="G23" s="14">
+        <v>1</v>
+      </c>
+      <c r="H23" s="15">
+        <v>0</v>
       </c>
       <c r="I23" s="14">
         <v>2</v>
       </c>
       <c r="J23" s="14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K23" s="15">
-        <v>0</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="L23" s="15">
         <v>100</v>
@@ -1275,34 +1275,34 @@
         <v>31</v>
       </c>
       <c r="C24" s="14">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="D24" s="14">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="E24" s="15">
-        <v>0</v>
+        <v>-44.827586206896</v>
       </c>
       <c r="F24" s="14">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="G24" s="14">
-        <v>104</v>
+        <v>110</v>
       </c>
       <c r="H24" s="15">
-        <v>-24.038461538461</v>
+        <v>-32.727272727272</v>
       </c>
       <c r="I24" s="14">
-        <v>206</v>
+        <v>223</v>
       </c>
       <c r="J24" s="14">
-        <v>307</v>
+        <v>336</v>
       </c>
       <c r="K24" s="15">
-        <v>-32.899022801302</v>
+        <v>-33.630952380952</v>
       </c>
       <c r="L24" s="15">
-        <v>-38.872403560830</v>
+        <v>-39.071038251366</v>
       </c>
       <c r="M24" s="13" t="s">
         <v>21</v>
@@ -1316,34 +1316,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="14">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D25" s="14">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="E25" s="15">
-        <v>0</v>
+        <v>-30</v>
       </c>
       <c r="F25" s="14">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="G25" s="14">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="H25" s="15">
-        <v>-23.880597014925</v>
+        <v>-29.577464788732</v>
       </c>
       <c r="I25" s="14">
-        <v>146</v>
+        <v>160</v>
       </c>
       <c r="J25" s="14">
-        <v>207</v>
+        <v>227</v>
       </c>
       <c r="K25" s="15">
-        <v>-29.468599033816</v>
+        <v>-29.515418502202</v>
       </c>
       <c r="L25" s="15">
-        <v>-38.655462184873</v>
+        <v>-37.743190661478</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1357,34 +1357,34 @@
         <v>33</v>
       </c>
       <c r="C26" s="14">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="D26" s="14">
-        <v>17</v>
+        <v>6</v>
       </c>
       <c r="E26" s="15">
-        <v>-58.823529411764</v>
+        <v>66.666666666666</v>
       </c>
       <c r="F26" s="14">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="G26" s="14">
         <v>47</v>
       </c>
       <c r="H26" s="15">
-        <v>4.255319148936</v>
+        <v>-8.510638297872</v>
       </c>
       <c r="I26" s="14">
-        <v>108</v>
+        <v>118</v>
       </c>
       <c r="J26" s="14">
-        <v>97</v>
+        <v>103</v>
       </c>
       <c r="K26" s="15">
-        <v>11.340206185567</v>
+        <v>14.563106796116</v>
       </c>
       <c r="L26" s="15">
-        <v>-10</v>
+        <v>-13.868613138686</v>
       </c>
       <c r="M26" s="13" t="s">
         <v>21</v>
@@ -1397,35 +1397,35 @@
       <c r="A27" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="C27" s="14">
-        <v>1</v>
-      </c>
-      <c r="D27" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E27" s="13" t="s">
-        <v>21</v>
+      <c r="C27" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D27" s="14">
+        <v>5</v>
+      </c>
+      <c r="E27" s="15">
+        <v>-100</v>
       </c>
       <c r="F27" s="14">
         <v>1</v>
       </c>
       <c r="G27" s="14">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="H27" s="15">
-        <v>0</v>
+        <v>-83.333333333333</v>
       </c>
       <c r="I27" s="14">
         <v>8</v>
       </c>
       <c r="J27" s="14">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="K27" s="15">
+        <v>-11.111111111111</v>
+      </c>
+      <c r="L27" s="15">
         <v>100</v>
-      </c>
-      <c r="L27" s="15">
-        <v>300</v>
       </c>
       <c r="M27" s="13" t="s">
         <v>21</v>
@@ -1441,32 +1441,32 @@
       <c r="C28" s="14">
         <v>1</v>
       </c>
-      <c r="D28" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E28" s="13" t="s">
-        <v>21</v>
+      <c r="D28" s="14">
+        <v>1</v>
+      </c>
+      <c r="E28" s="15">
+        <v>0</v>
       </c>
       <c r="F28" s="14">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="G28" s="14">
         <v>5</v>
       </c>
       <c r="H28" s="15">
-        <v>80</v>
+        <v>0</v>
       </c>
       <c r="I28" s="14">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="J28" s="14">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K28" s="15">
         <v>0</v>
       </c>
       <c r="L28" s="15">
-        <v>55.555555555555</v>
+        <v>66.666666666666</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1482,32 +1482,32 @@
       <c r="C29" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D29" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E29" s="13" t="s">
-        <v>21</v>
+      <c r="D29" s="14">
+        <v>1</v>
+      </c>
+      <c r="E29" s="15">
+        <v>-100</v>
       </c>
       <c r="F29" s="14">
         <v>1</v>
       </c>
-      <c r="G29" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="H29" s="13" t="s">
-        <v>21</v>
+      <c r="G29" s="14">
+        <v>1</v>
+      </c>
+      <c r="H29" s="15">
+        <v>0</v>
       </c>
       <c r="I29" s="14">
         <v>1</v>
       </c>
-      <c r="J29" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="K29" s="13" t="s">
-        <v>21</v>
-      </c>
-      <c r="L29" s="13" t="s">
-        <v>21</v>
+      <c r="J29" s="14">
+        <v>1</v>
+      </c>
+      <c r="K29" s="15">
+        <v>0</v>
+      </c>
+      <c r="L29" s="15">
+        <v>0</v>
       </c>
       <c r="M29" s="13" t="s">
         <v>21</v>
@@ -1523,32 +1523,32 @@
       <c r="C30" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D30" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E30" s="13" t="s">
-        <v>21</v>
+      <c r="D30" s="14">
+        <v>1</v>
+      </c>
+      <c r="E30" s="15">
+        <v>-100</v>
       </c>
       <c r="F30" s="14">
         <v>1</v>
       </c>
-      <c r="G30" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="H30" s="13" t="s">
-        <v>21</v>
+      <c r="G30" s="14">
+        <v>1</v>
+      </c>
+      <c r="H30" s="15">
+        <v>0</v>
       </c>
       <c r="I30" s="14">
         <v>1</v>
       </c>
-      <c r="J30" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="K30" s="13" t="s">
-        <v>21</v>
-      </c>
-      <c r="L30" s="13" t="s">
-        <v>21</v>
+      <c r="J30" s="14">
+        <v>1</v>
+      </c>
+      <c r="K30" s="15">
+        <v>0</v>
+      </c>
+      <c r="L30" s="15">
+        <v>0</v>
       </c>
       <c r="M30" s="13" t="s">
         <v>21</v>

--- a/data/source/weekly/cs-en-us-121pct.xlsx
+++ b/data/source/weekly/cs-en-us-121pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">12</t>
+      <t xml:space="preserve">13</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/16/2026</t>
+      <t xml:space="preserve">3/23/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/22/2026</t>
+      <t xml:space="preserve">3/29/2026</t>
     </r>
   </si>
   <si>
@@ -905,35 +905,35 @@
       <c r="A15" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="C15" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="D15" s="14">
+      <c r="C15" s="14">
+        <v>1</v>
+      </c>
+      <c r="D15" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E15" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="F15" s="14">
+        <v>1</v>
+      </c>
+      <c r="G15" s="14">
         <v>4</v>
       </c>
-      <c r="E15" s="15">
-        <v>-100</v>
-      </c>
-      <c r="F15" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="G15" s="14">
-        <v>5</v>
-      </c>
       <c r="H15" s="15">
-        <v>-100</v>
+        <v>-75</v>
       </c>
       <c r="I15" s="14">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J15" s="14">
         <v>8</v>
       </c>
       <c r="K15" s="15">
-        <v>-25</v>
+        <v>-12.5</v>
       </c>
       <c r="L15" s="15">
-        <v>200</v>
+        <v>250</v>
       </c>
       <c r="M15" s="13" t="s">
         <v>21</v>
@@ -947,34 +947,34 @@
         <v>23</v>
       </c>
       <c r="C16" s="14">
+        <v>1</v>
+      </c>
+      <c r="D16" s="14">
+        <v>1</v>
+      </c>
+      <c r="E16" s="15">
+        <v>0</v>
+      </c>
+      <c r="F16" s="14">
+        <v>6</v>
+      </c>
+      <c r="G16" s="14">
         <v>2</v>
       </c>
-      <c r="D16" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E16" s="13" t="s">
-        <v>21</v>
-      </c>
-      <c r="F16" s="14">
-        <v>5</v>
-      </c>
-      <c r="G16" s="14">
-        <v>3</v>
-      </c>
       <c r="H16" s="15">
-        <v>66.666666666666</v>
+        <v>200</v>
       </c>
       <c r="I16" s="14">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J16" s="14">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="K16" s="15">
-        <v>18.181818181818</v>
+        <v>16.666666666666</v>
       </c>
       <c r="L16" s="15">
-        <v>-7.142857142857</v>
+        <v>-17.647058823529</v>
       </c>
       <c r="M16" s="13" t="s">
         <v>21</v>
@@ -988,34 +988,34 @@
         <v>24</v>
       </c>
       <c r="C17" s="14">
+        <v>8</v>
+      </c>
+      <c r="D17" s="14">
         <v>6</v>
       </c>
-      <c r="D17" s="14">
-        <v>4</v>
-      </c>
       <c r="E17" s="15">
-        <v>50</v>
+        <v>33.333333333333</v>
       </c>
       <c r="F17" s="14">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="G17" s="14">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="H17" s="15">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="I17" s="14">
-        <v>60</v>
+        <v>68</v>
       </c>
       <c r="J17" s="14">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="K17" s="15">
-        <v>39.534883720930</v>
+        <v>38.775510204081</v>
       </c>
       <c r="L17" s="15">
-        <v>22.448979591836</v>
+        <v>30.769230769230</v>
       </c>
       <c r="M17" s="13" t="s">
         <v>21</v>
@@ -1031,32 +1031,32 @@
       <c r="C18" s="14">
         <v>1</v>
       </c>
-      <c r="D18" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E18" s="13" t="s">
-        <v>21</v>
+      <c r="D18" s="14">
+        <v>1</v>
+      </c>
+      <c r="E18" s="15">
+        <v>0</v>
       </c>
       <c r="F18" s="14">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G18" s="14">
         <v>4</v>
       </c>
       <c r="H18" s="15">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="I18" s="14">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="J18" s="14">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="K18" s="15">
-        <v>-56.521739130434</v>
+        <v>-54.166666666666</v>
       </c>
       <c r="L18" s="15">
-        <v>-23.076923076923</v>
+        <v>-21.428571428571</v>
       </c>
       <c r="M18" s="13" t="s">
         <v>21</v>
@@ -1070,34 +1070,34 @@
         <v>26</v>
       </c>
       <c r="C19" s="14">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="D19" s="14">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E19" s="15">
-        <v>125</v>
+        <v>0</v>
       </c>
       <c r="F19" s="14">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="G19" s="14">
-        <v>35</v>
+        <v>26</v>
       </c>
       <c r="H19" s="15">
-        <v>-22.857142857142</v>
+        <v>7.692307692307</v>
       </c>
       <c r="I19" s="14">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="J19" s="14">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="K19" s="15">
-        <v>-10.588235294117</v>
+        <v>-10</v>
       </c>
       <c r="L19" s="15">
-        <v>-7.317073170731</v>
+        <v>-6.896551724137</v>
       </c>
       <c r="M19" s="13" t="s">
         <v>21</v>
@@ -1111,7 +1111,7 @@
         <v>27</v>
       </c>
       <c r="C20" s="14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D20" s="13" t="s">
         <v>20</v>
@@ -1123,10 +1123,10 @@
         <v>4</v>
       </c>
       <c r="G20" s="14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H20" s="15">
-        <v>100</v>
+        <v>300</v>
       </c>
       <c r="I20" s="14">
         <v>12</v>
@@ -1138,7 +1138,7 @@
         <v>-40</v>
       </c>
       <c r="L20" s="15">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="M20" s="13" t="s">
         <v>21</v>
@@ -1152,34 +1152,34 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="D21" s="17">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E21" s="18">
-        <v>66.666666666666</v>
+        <v>30.769230769230</v>
       </c>
       <c r="F21" s="17">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="G21" s="17">
-        <v>62</v>
+        <v>52</v>
       </c>
       <c r="H21" s="18">
-        <v>6.451612903225</v>
+        <v>36.538461538461</v>
       </c>
       <c r="I21" s="17">
-        <v>177</v>
+        <v>193</v>
       </c>
       <c r="J21" s="17">
-        <v>190</v>
+        <v>203</v>
       </c>
       <c r="K21" s="18">
-        <v>-6.842105263157</v>
+        <v>-4.926108374384</v>
       </c>
       <c r="L21" s="18">
-        <v>6.626506024096</v>
+        <v>7.222222222222</v>
       </c>
       <c r="M21" s="19" t="s">
         <v>21</v>
@@ -1236,11 +1236,11 @@
       <c r="C23" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D23" s="14">
-        <v>1</v>
-      </c>
-      <c r="E23" s="15">
-        <v>-100</v>
+      <c r="D23" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E23" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F23" s="14">
         <v>1</v>
@@ -1275,34 +1275,34 @@
         <v>31</v>
       </c>
       <c r="C24" s="14">
-        <v>16</v>
+        <v>27</v>
       </c>
       <c r="D24" s="14">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E24" s="15">
-        <v>-44.827586206896</v>
+        <v>-10</v>
       </c>
       <c r="F24" s="14">
-        <v>74</v>
+        <v>87</v>
       </c>
       <c r="G24" s="14">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="H24" s="15">
-        <v>-32.727272727272</v>
+        <v>-18.691588785046</v>
       </c>
       <c r="I24" s="14">
-        <v>223</v>
+        <v>250</v>
       </c>
       <c r="J24" s="14">
-        <v>336</v>
+        <v>366</v>
       </c>
       <c r="K24" s="15">
-        <v>-33.630952380952</v>
+        <v>-31.693989071038</v>
       </c>
       <c r="L24" s="15">
-        <v>-39.071038251366</v>
+        <v>-36.548223350253</v>
       </c>
       <c r="M24" s="13" t="s">
         <v>21</v>
@@ -1316,34 +1316,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="14">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="D25" s="14">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="E25" s="15">
-        <v>-30</v>
+        <v>-64</v>
       </c>
       <c r="F25" s="14">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="G25" s="14">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="H25" s="15">
-        <v>-29.577464788732</v>
+        <v>-36</v>
       </c>
       <c r="I25" s="14">
-        <v>160</v>
+        <v>169</v>
       </c>
       <c r="J25" s="14">
-        <v>227</v>
+        <v>252</v>
       </c>
       <c r="K25" s="15">
-        <v>-29.515418502202</v>
+        <v>-32.936507936507</v>
       </c>
       <c r="L25" s="15">
-        <v>-37.743190661478</v>
+        <v>-38.321167883211</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1360,31 +1360,31 @@
         <v>10</v>
       </c>
       <c r="D26" s="14">
-        <v>6</v>
+        <v>18</v>
       </c>
       <c r="E26" s="15">
-        <v>66.666666666666</v>
+        <v>-44.444444444444</v>
       </c>
       <c r="F26" s="14">
-        <v>43</v>
+        <v>36</v>
       </c>
       <c r="G26" s="14">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="H26" s="15">
-        <v>-8.510638297872</v>
+        <v>-32.075471698113</v>
       </c>
       <c r="I26" s="14">
-        <v>118</v>
+        <v>129</v>
       </c>
       <c r="J26" s="14">
-        <v>103</v>
+        <v>121</v>
       </c>
       <c r="K26" s="15">
-        <v>14.563106796116</v>
+        <v>6.611570247933</v>
       </c>
       <c r="L26" s="15">
-        <v>-13.868613138686</v>
+        <v>-15.131578947368</v>
       </c>
       <c r="M26" s="13" t="s">
         <v>21</v>
@@ -1397,35 +1397,35 @@
       <c r="A27" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="C27" s="13" t="s">
-        <v>20</v>
+      <c r="C27" s="14">
+        <v>3</v>
       </c>
       <c r="D27" s="14">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E27" s="15">
-        <v>-100</v>
+        <v>200</v>
       </c>
       <c r="F27" s="14">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G27" s="14">
         <v>6</v>
       </c>
       <c r="H27" s="15">
-        <v>-83.333333333333</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="I27" s="14">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="J27" s="14">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K27" s="15">
-        <v>-11.111111111111</v>
+        <v>10</v>
       </c>
       <c r="L27" s="15">
-        <v>100</v>
+        <v>175</v>
       </c>
       <c r="M27" s="13" t="s">
         <v>21</v>
@@ -1448,25 +1448,25 @@
         <v>0</v>
       </c>
       <c r="F28" s="14">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G28" s="14">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="H28" s="15">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="I28" s="14">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="J28" s="14">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="K28" s="15">
         <v>0</v>
       </c>
       <c r="L28" s="15">
-        <v>66.666666666666</v>
+        <v>77.777777777777</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1482,11 +1482,11 @@
       <c r="C29" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D29" s="14">
-        <v>1</v>
-      </c>
-      <c r="E29" s="15">
-        <v>-100</v>
+      <c r="D29" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E29" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F29" s="14">
         <v>1</v>
@@ -1523,11 +1523,11 @@
       <c r="C30" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D30" s="14">
-        <v>1</v>
-      </c>
-      <c r="E30" s="15">
-        <v>-100</v>
+      <c r="D30" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E30" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F30" s="14">
         <v>1</v>

--- a/data/source/weekly/cs-en-us-121pct.xlsx
+++ b/data/source/weekly/cs-en-us-121pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">13</t>
+      <t xml:space="preserve">14</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/23/2026</t>
+      <t xml:space="preserve">3/30/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/29/2026</t>
+      <t xml:space="preserve">4/5/2026</t>
     </r>
   </si>
   <si>
@@ -905,8 +905,8 @@
       <c r="A15" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="C15" s="14">
-        <v>1</v>
+      <c r="C15" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D15" s="13" t="s">
         <v>20</v>
@@ -949,32 +949,32 @@
       <c r="C16" s="14">
         <v>1</v>
       </c>
-      <c r="D16" s="14">
-        <v>1</v>
-      </c>
-      <c r="E16" s="15">
-        <v>0</v>
+      <c r="D16" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E16" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F16" s="14">
         <v>6</v>
       </c>
       <c r="G16" s="14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H16" s="15">
-        <v>200</v>
+        <v>500</v>
       </c>
       <c r="I16" s="14">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="J16" s="14">
         <v>12</v>
       </c>
       <c r="K16" s="15">
-        <v>16.666666666666</v>
+        <v>25</v>
       </c>
       <c r="L16" s="15">
-        <v>-17.647058823529</v>
+        <v>-28.571428571428</v>
       </c>
       <c r="M16" s="13" t="s">
         <v>21</v>
@@ -988,34 +988,34 @@
         <v>24</v>
       </c>
       <c r="C17" s="14">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D17" s="14">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E17" s="15">
-        <v>33.333333333333</v>
+        <v>40</v>
       </c>
       <c r="F17" s="14">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="G17" s="14">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="H17" s="15">
-        <v>80</v>
+        <v>76.470588235294</v>
       </c>
       <c r="I17" s="14">
-        <v>68</v>
+        <v>75</v>
       </c>
       <c r="J17" s="14">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="K17" s="15">
-        <v>38.775510204081</v>
+        <v>38.888888888888</v>
       </c>
       <c r="L17" s="15">
-        <v>30.769230769230</v>
+        <v>38.888888888888</v>
       </c>
       <c r="M17" s="13" t="s">
         <v>21</v>
@@ -1032,31 +1032,31 @@
         <v>1</v>
       </c>
       <c r="D18" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E18" s="15">
-        <v>0</v>
+        <v>-50</v>
       </c>
       <c r="F18" s="14">
         <v>5</v>
       </c>
       <c r="G18" s="14">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H18" s="15">
-        <v>25</v>
+        <v>66.666666666666</v>
       </c>
       <c r="I18" s="14">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="J18" s="14">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="K18" s="15">
-        <v>-54.166666666666</v>
+        <v>-53.846153846153</v>
       </c>
       <c r="L18" s="15">
-        <v>-21.428571428571</v>
+        <v>-14.285714285714</v>
       </c>
       <c r="M18" s="13" t="s">
         <v>21</v>
@@ -1070,34 +1070,34 @@
         <v>26</v>
       </c>
       <c r="C19" s="14">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="D19" s="14">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="E19" s="15">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="F19" s="14">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="G19" s="14">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="H19" s="15">
-        <v>7.692307692307</v>
+        <v>3.448275862068</v>
       </c>
       <c r="I19" s="14">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="J19" s="14">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="K19" s="15">
-        <v>-10</v>
+        <v>-8</v>
       </c>
       <c r="L19" s="15">
-        <v>-6.896551724137</v>
+        <v>-1.075268817204</v>
       </c>
       <c r="M19" s="13" t="s">
         <v>21</v>
@@ -1111,7 +1111,7 @@
         <v>27</v>
       </c>
       <c r="C20" s="14">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D20" s="13" t="s">
         <v>20</v>
@@ -1120,25 +1120,25 @@
         <v>21</v>
       </c>
       <c r="F20" s="14">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="G20" s="14">
         <v>1</v>
       </c>
       <c r="H20" s="15">
-        <v>300</v>
+        <v>700</v>
       </c>
       <c r="I20" s="14">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="J20" s="14">
         <v>20</v>
       </c>
       <c r="K20" s="15">
-        <v>-40</v>
+        <v>-20</v>
       </c>
       <c r="L20" s="15">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="M20" s="13" t="s">
         <v>21</v>
@@ -1152,34 +1152,34 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
+        <v>24</v>
+      </c>
+      <c r="D21" s="17">
         <v>17</v>
       </c>
-      <c r="D21" s="17">
-        <v>13</v>
-      </c>
       <c r="E21" s="18">
-        <v>30.769230769230</v>
+        <v>41.176470588235</v>
       </c>
       <c r="F21" s="17">
-        <v>71</v>
+        <v>80</v>
       </c>
       <c r="G21" s="17">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="H21" s="18">
-        <v>36.538461538461</v>
+        <v>45.454545454545</v>
       </c>
       <c r="I21" s="17">
-        <v>193</v>
+        <v>217</v>
       </c>
       <c r="J21" s="17">
-        <v>203</v>
+        <v>220</v>
       </c>
       <c r="K21" s="18">
-        <v>-4.926108374384</v>
+        <v>-1.363636363636</v>
       </c>
       <c r="L21" s="18">
-        <v>7.222222222222</v>
+        <v>11.855670103092</v>
       </c>
       <c r="M21" s="19" t="s">
         <v>21</v>
@@ -1261,7 +1261,7 @@
         <v>-33.333333333333</v>
       </c>
       <c r="L23" s="15">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="M23" s="13" t="s">
         <v>21</v>
@@ -1275,34 +1275,34 @@
         <v>31</v>
       </c>
       <c r="C24" s="14">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="D24" s="14">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="E24" s="15">
-        <v>-10</v>
+        <v>-35.714285714285</v>
       </c>
       <c r="F24" s="14">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="G24" s="14">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="H24" s="15">
-        <v>-18.691588785046</v>
+        <v>-23.148148148148</v>
       </c>
       <c r="I24" s="14">
-        <v>250</v>
+        <v>268</v>
       </c>
       <c r="J24" s="14">
-        <v>366</v>
+        <v>394</v>
       </c>
       <c r="K24" s="15">
-        <v>-31.693989071038</v>
+        <v>-31.979695431472</v>
       </c>
       <c r="L24" s="15">
-        <v>-36.548223350253</v>
+        <v>-36.038186157517</v>
       </c>
       <c r="M24" s="13" t="s">
         <v>21</v>
@@ -1319,31 +1319,31 @@
         <v>9</v>
       </c>
       <c r="D25" s="14">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="E25" s="15">
-        <v>-64</v>
+        <v>-40</v>
       </c>
       <c r="F25" s="14">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="G25" s="14">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="H25" s="15">
-        <v>-36</v>
+        <v>-38.356164383561</v>
       </c>
       <c r="I25" s="14">
-        <v>169</v>
+        <v>178</v>
       </c>
       <c r="J25" s="14">
-        <v>252</v>
+        <v>267</v>
       </c>
       <c r="K25" s="15">
-        <v>-32.936507936507</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="L25" s="15">
-        <v>-38.321167883211</v>
+        <v>-39.249146757679</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1357,34 +1357,34 @@
         <v>33</v>
       </c>
       <c r="C26" s="14">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D26" s="14">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="E26" s="15">
-        <v>-44.444444444444</v>
+        <v>-18.181818181818</v>
       </c>
       <c r="F26" s="14">
         <v>36</v>
       </c>
       <c r="G26" s="14">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H26" s="15">
-        <v>-32.075471698113</v>
+        <v>-30.769230769230</v>
       </c>
       <c r="I26" s="14">
-        <v>129</v>
+        <v>138</v>
       </c>
       <c r="J26" s="14">
-        <v>121</v>
+        <v>132</v>
       </c>
       <c r="K26" s="15">
-        <v>6.611570247933</v>
+        <v>4.545454545454</v>
       </c>
       <c r="L26" s="15">
-        <v>-15.131578947368</v>
+        <v>-13.207547169811</v>
       </c>
       <c r="M26" s="13" t="s">
         <v>21</v>
@@ -1397,14 +1397,14 @@
       <c r="A27" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="C27" s="14">
-        <v>3</v>
-      </c>
-      <c r="D27" s="14">
-        <v>1</v>
-      </c>
-      <c r="E27" s="15">
-        <v>200</v>
+      <c r="C27" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D27" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E27" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F27" s="14">
         <v>4</v>
@@ -1438,35 +1438,35 @@
       <c r="A28" s="13" t="s">
         <v>35</v>
       </c>
-      <c r="C28" s="14">
-        <v>1</v>
+      <c r="C28" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D28" s="14">
         <v>1</v>
       </c>
       <c r="E28" s="15">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="F28" s="14">
         <v>3</v>
       </c>
       <c r="G28" s="14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H28" s="15">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="I28" s="14">
         <v>16</v>
       </c>
       <c r="J28" s="14">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K28" s="15">
-        <v>0</v>
+        <v>-5.882352941176</v>
       </c>
       <c r="L28" s="15">
-        <v>77.777777777777</v>
+        <v>60</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1488,14 +1488,14 @@
       <c r="E29" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="F29" s="14">
-        <v>1</v>
+      <c r="F29" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="G29" s="14">
         <v>1</v>
       </c>
       <c r="H29" s="15">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="I29" s="14">
         <v>1</v>
@@ -1529,14 +1529,14 @@
       <c r="E30" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="F30" s="14">
-        <v>1</v>
+      <c r="F30" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="G30" s="14">
         <v>1</v>
       </c>
       <c r="H30" s="15">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="I30" s="14">
         <v>1</v>
@@ -1570,8 +1570,8 @@
       <c r="E31" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="F31" s="14">
-        <v>1</v>
+      <c r="F31" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="G31" s="13" t="s">
         <v>20</v>

--- a/data/source/weekly/cs-en-us-121pct.xlsx
+++ b/data/source/weekly/cs-en-us-121pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">14</t>
+      <t xml:space="preserve">15</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/30/2026</t>
+      <t xml:space="preserve">4/6/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">4/5/2026</t>
+      <t xml:space="preserve">4/12/2026</t>
     </r>
   </si>
   <si>
@@ -908,29 +908,29 @@
       <c r="C15" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D15" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E15" s="13" t="s">
-        <v>21</v>
+      <c r="D15" s="14">
+        <v>2</v>
+      </c>
+      <c r="E15" s="15">
+        <v>-100</v>
       </c>
       <c r="F15" s="14">
         <v>1</v>
       </c>
       <c r="G15" s="14">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="H15" s="15">
-        <v>-75</v>
+        <v>-83.333333333333</v>
       </c>
       <c r="I15" s="14">
         <v>7</v>
       </c>
       <c r="J15" s="14">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="K15" s="15">
-        <v>-12.5</v>
+        <v>-30</v>
       </c>
       <c r="L15" s="15">
         <v>250</v>
@@ -946,35 +946,35 @@
       <c r="A16" s="13" t="s">
         <v>23</v>
       </c>
-      <c r="C16" s="14">
+      <c r="C16" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D16" s="14">
         <v>1</v>
       </c>
-      <c r="D16" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E16" s="13" t="s">
-        <v>21</v>
+      <c r="E16" s="15">
+        <v>-100</v>
       </c>
       <c r="F16" s="14">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="G16" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H16" s="15">
-        <v>500</v>
+        <v>100</v>
       </c>
       <c r="I16" s="14">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="J16" s="14">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K16" s="15">
-        <v>25</v>
+        <v>23.076923076923</v>
       </c>
       <c r="L16" s="15">
-        <v>-28.571428571428</v>
+        <v>-27.272727272727</v>
       </c>
       <c r="M16" s="13" t="s">
         <v>21</v>
@@ -988,34 +988,34 @@
         <v>24</v>
       </c>
       <c r="C17" s="14">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="D17" s="14">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E17" s="15">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="F17" s="14">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="G17" s="14">
         <v>17</v>
       </c>
       <c r="H17" s="15">
-        <v>76.470588235294</v>
+        <v>41.176470588235</v>
       </c>
       <c r="I17" s="14">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="J17" s="14">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="K17" s="15">
-        <v>38.888888888888</v>
+        <v>39.285714285714</v>
       </c>
       <c r="L17" s="15">
-        <v>38.888888888888</v>
+        <v>36.842105263157</v>
       </c>
       <c r="M17" s="13" t="s">
         <v>21</v>
@@ -1029,34 +1029,34 @@
         <v>25</v>
       </c>
       <c r="C18" s="14">
-        <v>1</v>
-      </c>
-      <c r="D18" s="14">
-        <v>2</v>
-      </c>
-      <c r="E18" s="15">
-        <v>-50</v>
+        <v>3</v>
+      </c>
+      <c r="D18" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E18" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F18" s="14">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G18" s="14">
         <v>3</v>
       </c>
       <c r="H18" s="15">
-        <v>66.666666666666</v>
+        <v>100</v>
       </c>
       <c r="I18" s="14">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="J18" s="14">
         <v>26</v>
       </c>
       <c r="K18" s="15">
-        <v>-53.846153846153</v>
+        <v>-42.307692307692</v>
       </c>
       <c r="L18" s="15">
-        <v>-14.285714285714</v>
+        <v>-6.25</v>
       </c>
       <c r="M18" s="13" t="s">
         <v>21</v>
@@ -1070,34 +1070,34 @@
         <v>26</v>
       </c>
       <c r="C19" s="14">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="D19" s="14">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="E19" s="15">
-        <v>10</v>
+        <v>150</v>
       </c>
       <c r="F19" s="14">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="G19" s="14">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="H19" s="15">
-        <v>3.448275862068</v>
+        <v>60</v>
       </c>
       <c r="I19" s="14">
-        <v>92</v>
+        <v>107</v>
       </c>
       <c r="J19" s="14">
-        <v>100</v>
+        <v>106</v>
       </c>
       <c r="K19" s="15">
-        <v>-8</v>
+        <v>0.943396226415</v>
       </c>
       <c r="L19" s="15">
-        <v>-1.075268817204</v>
+        <v>11.458333333333</v>
       </c>
       <c r="M19" s="13" t="s">
         <v>21</v>
@@ -1111,7 +1111,7 @@
         <v>27</v>
       </c>
       <c r="C20" s="14">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D20" s="13" t="s">
         <v>20</v>
@@ -1120,25 +1120,25 @@
         <v>21</v>
       </c>
       <c r="F20" s="14">
-        <v>8</v>
-      </c>
-      <c r="G20" s="14">
-        <v>1</v>
-      </c>
-      <c r="H20" s="15">
-        <v>700</v>
+        <v>7</v>
+      </c>
+      <c r="G20" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="H20" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="I20" s="14">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J20" s="14">
         <v>20</v>
       </c>
       <c r="K20" s="15">
-        <v>-20</v>
+        <v>-15</v>
       </c>
       <c r="L20" s="15">
-        <v>60</v>
+        <v>21.428571428571</v>
       </c>
       <c r="M20" s="13" t="s">
         <v>21</v>
@@ -1152,34 +1152,34 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="D21" s="17">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="E21" s="18">
-        <v>41.176470588235</v>
+        <v>100</v>
       </c>
       <c r="F21" s="17">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="G21" s="17">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="H21" s="18">
-        <v>45.454545454545</v>
+        <v>54.716981132075</v>
       </c>
       <c r="I21" s="17">
-        <v>217</v>
+        <v>240</v>
       </c>
       <c r="J21" s="17">
-        <v>220</v>
+        <v>231</v>
       </c>
       <c r="K21" s="18">
-        <v>-1.363636363636</v>
+        <v>3.896103896103</v>
       </c>
       <c r="L21" s="18">
-        <v>11.855670103092</v>
+        <v>15.942028985507</v>
       </c>
       <c r="M21" s="19" t="s">
         <v>21</v>
@@ -1242,14 +1242,14 @@
       <c r="E23" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="F23" s="14">
-        <v>1</v>
+      <c r="F23" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="G23" s="14">
         <v>1</v>
       </c>
       <c r="H23" s="15">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="I23" s="14">
         <v>2</v>
@@ -1261,7 +1261,7 @@
         <v>-33.333333333333</v>
       </c>
       <c r="L23" s="15">
-        <v>0</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="M23" s="13" t="s">
         <v>21</v>
@@ -1275,34 +1275,34 @@
         <v>31</v>
       </c>
       <c r="C24" s="14">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="D24" s="14">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="E24" s="15">
-        <v>-35.714285714285</v>
+        <v>20</v>
       </c>
       <c r="F24" s="14">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="G24" s="14">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="H24" s="15">
-        <v>-23.148148148148</v>
+        <v>-19.626168224299</v>
       </c>
       <c r="I24" s="14">
-        <v>268</v>
+        <v>292</v>
       </c>
       <c r="J24" s="14">
-        <v>394</v>
+        <v>414</v>
       </c>
       <c r="K24" s="15">
-        <v>-31.979695431472</v>
+        <v>-29.468599033816</v>
       </c>
       <c r="L24" s="15">
-        <v>-36.038186157517</v>
+        <v>-34.821428571428</v>
       </c>
       <c r="M24" s="13" t="s">
         <v>21</v>
@@ -1316,34 +1316,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="14">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="D25" s="14">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="E25" s="15">
-        <v>-40</v>
+        <v>62.5</v>
       </c>
       <c r="F25" s="14">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="G25" s="14">
-        <v>73</v>
+        <v>68</v>
       </c>
       <c r="H25" s="15">
-        <v>-38.356164383561</v>
+        <v>-35.294117647058</v>
       </c>
       <c r="I25" s="14">
-        <v>178</v>
+        <v>190</v>
       </c>
       <c r="J25" s="14">
-        <v>267</v>
+        <v>275</v>
       </c>
       <c r="K25" s="15">
-        <v>-33.333333333333</v>
+        <v>-30.909090909090</v>
       </c>
       <c r="L25" s="15">
-        <v>-39.249146757679</v>
+        <v>-38.511326860841</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1357,34 +1357,34 @@
         <v>33</v>
       </c>
       <c r="C26" s="14">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D26" s="14">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="E26" s="15">
-        <v>-18.181818181818</v>
+        <v>-53.333333333333</v>
       </c>
       <c r="F26" s="14">
         <v>36</v>
       </c>
       <c r="G26" s="14">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="H26" s="15">
-        <v>-30.769230769230</v>
+        <v>-28</v>
       </c>
       <c r="I26" s="14">
-        <v>138</v>
+        <v>145</v>
       </c>
       <c r="J26" s="14">
-        <v>132</v>
+        <v>147</v>
       </c>
       <c r="K26" s="15">
-        <v>4.545454545454</v>
+        <v>-1.360544217687</v>
       </c>
       <c r="L26" s="15">
-        <v>-13.207547169811</v>
+        <v>-15.697674418604</v>
       </c>
       <c r="M26" s="13" t="s">
         <v>21</v>
@@ -1400,32 +1400,32 @@
       <c r="C27" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D27" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E27" s="13" t="s">
-        <v>21</v>
+      <c r="D27" s="14">
+        <v>2</v>
+      </c>
+      <c r="E27" s="15">
+        <v>-100</v>
       </c>
       <c r="F27" s="14">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G27" s="14">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="H27" s="15">
-        <v>-33.333333333333</v>
+        <v>-62.5</v>
       </c>
       <c r="I27" s="14">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="J27" s="14">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="K27" s="15">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="L27" s="15">
-        <v>175</v>
+        <v>200</v>
       </c>
       <c r="M27" s="13" t="s">
         <v>21</v>
@@ -1442,31 +1442,31 @@
         <v>20</v>
       </c>
       <c r="D28" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E28" s="15">
         <v>-100</v>
       </c>
       <c r="F28" s="14">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G28" s="14">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="H28" s="15">
-        <v>0</v>
+        <v>-60</v>
       </c>
       <c r="I28" s="14">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="J28" s="14">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="K28" s="15">
-        <v>-5.882352941176</v>
+        <v>-21.052631578947</v>
       </c>
       <c r="L28" s="15">
-        <v>60</v>
+        <v>7.142857142857</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1620,8 +1620,8 @@
       <c r="A33" s="13" t="s">
         <v>40</v>
       </c>
-      <c r="C33" s="13" t="s">
-        <v>20</v>
+      <c r="C33" s="14">
+        <v>1</v>
       </c>
       <c r="D33" s="13" t="s">
         <v>20</v>
@@ -1629,8 +1629,8 @@
       <c r="E33" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="F33" s="13" t="s">
-        <v>20</v>
+      <c r="F33" s="14">
+        <v>1</v>
       </c>
       <c r="G33" s="13" t="s">
         <v>20</v>
@@ -1639,7 +1639,7 @@
         <v>21</v>
       </c>
       <c r="I33" s="14">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J33" s="13" t="s">
         <v>20</v>
@@ -1648,7 +1648,7 @@
         <v>21</v>
       </c>
       <c r="L33" s="15">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="M33" s="13" t="s">
         <v>21</v>

--- a/data/source/weekly/cs-en-us-121pct.xlsx
+++ b/data/source/weekly/cs-en-us-121pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">15</t>
+      <t xml:space="preserve">16</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">4/6/2026</t>
+      <t xml:space="preserve">4/13/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">4/12/2026</t>
+      <t xml:space="preserve">4/19/2026</t>
     </r>
   </si>
   <si>
@@ -905,35 +905,35 @@
       <c r="A15" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="C15" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="D15" s="14">
+      <c r="C15" s="14">
+        <v>1</v>
+      </c>
+      <c r="D15" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E15" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="F15" s="14">
         <v>2</v>
       </c>
-      <c r="E15" s="15">
-        <v>-100</v>
-      </c>
-      <c r="F15" s="14">
-        <v>1</v>
-      </c>
       <c r="G15" s="14">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="H15" s="15">
-        <v>-83.333333333333</v>
+        <v>0</v>
       </c>
       <c r="I15" s="14">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J15" s="14">
         <v>10</v>
       </c>
       <c r="K15" s="15">
-        <v>-30</v>
+        <v>-20</v>
       </c>
       <c r="L15" s="15">
-        <v>250</v>
+        <v>166.666666666667</v>
       </c>
       <c r="M15" s="13" t="s">
         <v>21</v>
@@ -946,35 +946,35 @@
       <c r="A16" s="13" t="s">
         <v>23</v>
       </c>
-      <c r="C16" s="13" t="s">
-        <v>20</v>
+      <c r="C16" s="14">
+        <v>2</v>
       </c>
       <c r="D16" s="14">
         <v>1</v>
       </c>
       <c r="E16" s="15">
-        <v>-100</v>
+        <v>100</v>
       </c>
       <c r="F16" s="14">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G16" s="14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H16" s="15">
-        <v>100</v>
+        <v>66.666666666666</v>
       </c>
       <c r="I16" s="14">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="J16" s="14">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K16" s="15">
-        <v>23.076923076923</v>
+        <v>35.714285714285</v>
       </c>
       <c r="L16" s="15">
-        <v>-27.272727272727</v>
+        <v>-26.923076923076</v>
       </c>
       <c r="M16" s="13" t="s">
         <v>21</v>
@@ -988,34 +988,34 @@
         <v>24</v>
       </c>
       <c r="C17" s="14">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D17" s="14">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E17" s="15">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="F17" s="14">
         <v>24</v>
       </c>
       <c r="G17" s="14">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="H17" s="15">
-        <v>41.176470588235</v>
+        <v>33.333333333333</v>
       </c>
       <c r="I17" s="14">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="J17" s="14">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="K17" s="15">
-        <v>39.285714285714</v>
+        <v>37.704918032786</v>
       </c>
       <c r="L17" s="15">
-        <v>36.842105263157</v>
+        <v>31.25</v>
       </c>
       <c r="M17" s="13" t="s">
         <v>21</v>
@@ -1029,7 +1029,7 @@
         <v>25</v>
       </c>
       <c r="C18" s="14">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D18" s="13" t="s">
         <v>20</v>
@@ -1038,25 +1038,25 @@
         <v>21</v>
       </c>
       <c r="F18" s="14">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G18" s="14">
         <v>3</v>
       </c>
       <c r="H18" s="15">
-        <v>100</v>
+        <v>133.333333333333</v>
       </c>
       <c r="I18" s="14">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="J18" s="14">
         <v>26</v>
       </c>
       <c r="K18" s="15">
-        <v>-42.307692307692</v>
+        <v>-34.615384615384</v>
       </c>
       <c r="L18" s="15">
-        <v>-6.25</v>
+        <v>0</v>
       </c>
       <c r="M18" s="13" t="s">
         <v>21</v>
@@ -1070,34 +1070,34 @@
         <v>26</v>
       </c>
       <c r="C19" s="14">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="D19" s="14">
         <v>6</v>
       </c>
       <c r="E19" s="15">
-        <v>150</v>
+        <v>33.333333333333</v>
       </c>
       <c r="F19" s="14">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="G19" s="14">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="H19" s="15">
-        <v>60</v>
+        <v>40.740740740740</v>
       </c>
       <c r="I19" s="14">
-        <v>107</v>
+        <v>114</v>
       </c>
       <c r="J19" s="14">
-        <v>106</v>
+        <v>112</v>
       </c>
       <c r="K19" s="15">
-        <v>0.943396226415</v>
+        <v>1.785714285714</v>
       </c>
       <c r="L19" s="15">
-        <v>11.458333333333</v>
+        <v>11.764705882352</v>
       </c>
       <c r="M19" s="13" t="s">
         <v>21</v>
@@ -1129,16 +1129,16 @@
         <v>21</v>
       </c>
       <c r="I20" s="14">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J20" s="14">
         <v>20</v>
       </c>
       <c r="K20" s="15">
-        <v>-15</v>
+        <v>-10</v>
       </c>
       <c r="L20" s="15">
-        <v>21.428571428571</v>
+        <v>20</v>
       </c>
       <c r="M20" s="13" t="s">
         <v>21</v>
@@ -1152,34 +1152,34 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="D21" s="17">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E21" s="18">
-        <v>100</v>
+        <v>66.666666666666</v>
       </c>
       <c r="F21" s="17">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="G21" s="17">
         <v>53</v>
       </c>
       <c r="H21" s="18">
-        <v>54.716981132075</v>
+        <v>56.603773584905</v>
       </c>
       <c r="I21" s="17">
-        <v>240</v>
+        <v>260</v>
       </c>
       <c r="J21" s="17">
-        <v>231</v>
+        <v>243</v>
       </c>
       <c r="K21" s="18">
-        <v>3.896103896103</v>
+        <v>6.995884773662</v>
       </c>
       <c r="L21" s="18">
-        <v>15.942028985507</v>
+        <v>14.537444933920</v>
       </c>
       <c r="M21" s="19" t="s">
         <v>21</v>
@@ -1233,35 +1233,35 @@
       <c r="A23" s="13" t="s">
         <v>30</v>
       </c>
-      <c r="C23" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="D23" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E23" s="13" t="s">
-        <v>21</v>
-      </c>
-      <c r="F23" s="13" t="s">
-        <v>20</v>
+      <c r="C23" s="14">
+        <v>1</v>
+      </c>
+      <c r="D23" s="14">
+        <v>2</v>
+      </c>
+      <c r="E23" s="15">
+        <v>-50</v>
+      </c>
+      <c r="F23" s="14">
+        <v>1</v>
       </c>
       <c r="G23" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H23" s="15">
-        <v>-100</v>
+        <v>-50</v>
       </c>
       <c r="I23" s="14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J23" s="14">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="K23" s="15">
-        <v>-33.333333333333</v>
+        <v>-40</v>
       </c>
       <c r="L23" s="15">
-        <v>-33.333333333333</v>
+        <v>0</v>
       </c>
       <c r="M23" s="13" t="s">
         <v>21</v>
@@ -1275,34 +1275,34 @@
         <v>31</v>
       </c>
       <c r="C24" s="14">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="D24" s="14">
-        <v>20</v>
+        <v>41</v>
       </c>
       <c r="E24" s="15">
-        <v>20</v>
+        <v>-53.658536585365</v>
       </c>
       <c r="F24" s="14">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="G24" s="14">
-        <v>107</v>
+        <v>119</v>
       </c>
       <c r="H24" s="15">
-        <v>-19.626168224299</v>
+        <v>-25.210084033613</v>
       </c>
       <c r="I24" s="14">
-        <v>292</v>
+        <v>311</v>
       </c>
       <c r="J24" s="14">
-        <v>414</v>
+        <v>455</v>
       </c>
       <c r="K24" s="15">
-        <v>-29.468599033816</v>
+        <v>-31.648351648351</v>
       </c>
       <c r="L24" s="15">
-        <v>-34.821428571428</v>
+        <v>-33.547008547008</v>
       </c>
       <c r="M24" s="13" t="s">
         <v>21</v>
@@ -1319,31 +1319,31 @@
         <v>13</v>
       </c>
       <c r="D25" s="14">
-        <v>8</v>
+        <v>32</v>
       </c>
       <c r="E25" s="15">
-        <v>62.5</v>
+        <v>-59.375</v>
       </c>
       <c r="F25" s="14">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="G25" s="14">
-        <v>68</v>
+        <v>80</v>
       </c>
       <c r="H25" s="15">
-        <v>-35.294117647058</v>
+        <v>-46.25</v>
       </c>
       <c r="I25" s="14">
-        <v>190</v>
+        <v>203</v>
       </c>
       <c r="J25" s="14">
-        <v>275</v>
+        <v>307</v>
       </c>
       <c r="K25" s="15">
-        <v>-30.909090909090</v>
+        <v>-33.876221498371</v>
       </c>
       <c r="L25" s="15">
-        <v>-38.511326860841</v>
+        <v>-37.345679012345</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1357,34 +1357,34 @@
         <v>33</v>
       </c>
       <c r="C26" s="14">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="D26" s="14">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="E26" s="15">
-        <v>-53.333333333333</v>
+        <v>-52.631578947368</v>
       </c>
       <c r="F26" s="14">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="G26" s="14">
-        <v>50</v>
+        <v>63</v>
       </c>
       <c r="H26" s="15">
-        <v>-28</v>
+        <v>-44.444444444444</v>
       </c>
       <c r="I26" s="14">
-        <v>145</v>
+        <v>154</v>
       </c>
       <c r="J26" s="14">
-        <v>147</v>
+        <v>166</v>
       </c>
       <c r="K26" s="15">
-        <v>-1.360544217687</v>
+        <v>-7.228915662650</v>
       </c>
       <c r="L26" s="15">
-        <v>-15.697674418604</v>
+        <v>-17.647058823529</v>
       </c>
       <c r="M26" s="13" t="s">
         <v>21</v>
@@ -1397,35 +1397,35 @@
       <c r="A27" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="C27" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="D27" s="14">
-        <v>2</v>
-      </c>
-      <c r="E27" s="15">
-        <v>-100</v>
+      <c r="C27" s="14">
+        <v>1</v>
+      </c>
+      <c r="D27" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E27" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F27" s="14">
+        <v>4</v>
+      </c>
+      <c r="G27" s="14">
         <v>3</v>
       </c>
-      <c r="G27" s="14">
-        <v>8</v>
-      </c>
       <c r="H27" s="15">
-        <v>-62.5</v>
+        <v>33.333333333333</v>
       </c>
       <c r="I27" s="14">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="J27" s="14">
         <v>12</v>
       </c>
       <c r="K27" s="15">
-        <v>0</v>
+        <v>8.333333333333</v>
       </c>
       <c r="L27" s="15">
-        <v>200</v>
+        <v>116.666666666667</v>
       </c>
       <c r="M27" s="13" t="s">
         <v>21</v>
@@ -1438,35 +1438,35 @@
       <c r="A28" s="13" t="s">
         <v>35</v>
       </c>
-      <c r="C28" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="D28" s="14">
-        <v>2</v>
-      </c>
-      <c r="E28" s="15">
-        <v>-100</v>
+      <c r="C28" s="14">
+        <v>1</v>
+      </c>
+      <c r="D28" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E28" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F28" s="14">
         <v>2</v>
       </c>
       <c r="G28" s="14">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H28" s="15">
-        <v>-60</v>
+        <v>-50</v>
       </c>
       <c r="I28" s="14">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="J28" s="14">
         <v>19</v>
       </c>
       <c r="K28" s="15">
-        <v>-21.052631578947</v>
+        <v>-15.789473684210</v>
       </c>
       <c r="L28" s="15">
-        <v>7.142857142857</v>
+        <v>14.285714285714</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1479,8 +1479,8 @@
       <c r="A29" s="13" t="s">
         <v>36</v>
       </c>
-      <c r="C29" s="13" t="s">
-        <v>20</v>
+      <c r="C29" s="14">
+        <v>1</v>
       </c>
       <c r="D29" s="13" t="s">
         <v>20</v>
@@ -1488,26 +1488,26 @@
       <c r="E29" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="F29" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="G29" s="14">
+      <c r="F29" s="14">
         <v>1</v>
       </c>
-      <c r="H29" s="15">
-        <v>-100</v>
+      <c r="G29" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="H29" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="I29" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J29" s="14">
         <v>1</v>
       </c>
       <c r="K29" s="15">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L29" s="15">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M29" s="13" t="s">
         <v>21</v>
@@ -1520,8 +1520,8 @@
       <c r="A30" s="13" t="s">
         <v>37</v>
       </c>
-      <c r="C30" s="13" t="s">
-        <v>20</v>
+      <c r="C30" s="14">
+        <v>1</v>
       </c>
       <c r="D30" s="13" t="s">
         <v>20</v>
@@ -1529,26 +1529,26 @@
       <c r="E30" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="F30" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="G30" s="14">
+      <c r="F30" s="14">
         <v>1</v>
       </c>
-      <c r="H30" s="15">
-        <v>-100</v>
+      <c r="G30" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="H30" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="I30" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J30" s="14">
         <v>1</v>
       </c>
       <c r="K30" s="15">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L30" s="15">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M30" s="13" t="s">
         <v>21</v>
@@ -1620,8 +1620,8 @@
       <c r="A33" s="13" t="s">
         <v>40</v>
       </c>
-      <c r="C33" s="14">
-        <v>1</v>
+      <c r="C33" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D33" s="13" t="s">
         <v>20</v>

--- a/data/source/weekly/cs-en-us-121pct.xlsx
+++ b/data/source/weekly/cs-en-us-121pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">16</t>
+      <t xml:space="preserve">17</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">4/13/2026</t>
+      <t xml:space="preserve">4/20/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">4/19/2026</t>
+      <t xml:space="preserve">4/26/2026</t>
     </r>
   </si>
   <si>
@@ -708,7 +708,7 @@
     <col min="5" max="5" width="7.433768" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="6.168446" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="7.433768" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="9.964413" bestFit="1" customWidth="1"/>
@@ -905,32 +905,32 @@
       <c r="A15" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="C15" s="14">
+      <c r="C15" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D15" s="14">
+        <v>2</v>
+      </c>
+      <c r="E15" s="15">
+        <v>-100</v>
+      </c>
+      <c r="F15" s="14">
         <v>1</v>
       </c>
-      <c r="D15" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E15" s="13" t="s">
-        <v>21</v>
-      </c>
-      <c r="F15" s="14">
-        <v>2</v>
-      </c>
       <c r="G15" s="14">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H15" s="15">
-        <v>0</v>
+        <v>-75</v>
       </c>
       <c r="I15" s="14">
         <v>8</v>
       </c>
       <c r="J15" s="14">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="K15" s="15">
-        <v>-20</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="L15" s="15">
         <v>166.666666666667</v>
@@ -946,35 +946,35 @@
       <c r="A16" s="13" t="s">
         <v>23</v>
       </c>
-      <c r="C16" s="14">
-        <v>2</v>
+      <c r="C16" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D16" s="14">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E16" s="15">
-        <v>100</v>
+        <v>-100</v>
       </c>
       <c r="F16" s="14">
         <v>5</v>
       </c>
       <c r="G16" s="14">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="H16" s="15">
-        <v>66.666666666666</v>
+        <v>0</v>
       </c>
       <c r="I16" s="14">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="J16" s="14">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="K16" s="15">
-        <v>35.714285714285</v>
+        <v>17.647058823529</v>
       </c>
       <c r="L16" s="15">
-        <v>-26.923076923076</v>
+        <v>-23.076923076923</v>
       </c>
       <c r="M16" s="13" t="s">
         <v>21</v>
@@ -988,34 +988,34 @@
         <v>24</v>
       </c>
       <c r="C17" s="14">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="D17" s="14">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E17" s="15">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="F17" s="14">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="G17" s="14">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="H17" s="15">
-        <v>33.333333333333</v>
+        <v>35.714285714285</v>
       </c>
       <c r="I17" s="14">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="J17" s="14">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="K17" s="15">
-        <v>37.704918032786</v>
+        <v>39.682539682539</v>
       </c>
       <c r="L17" s="15">
-        <v>31.25</v>
+        <v>31.343283582089</v>
       </c>
       <c r="M17" s="13" t="s">
         <v>21</v>
@@ -1031,32 +1031,32 @@
       <c r="C18" s="14">
         <v>2</v>
       </c>
-      <c r="D18" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E18" s="13" t="s">
-        <v>21</v>
+      <c r="D18" s="14">
+        <v>2</v>
+      </c>
+      <c r="E18" s="15">
+        <v>0</v>
       </c>
       <c r="F18" s="14">
         <v>7</v>
       </c>
       <c r="G18" s="14">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H18" s="15">
-        <v>133.333333333333</v>
+        <v>75</v>
       </c>
       <c r="I18" s="14">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J18" s="14">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="K18" s="15">
-        <v>-34.615384615384</v>
+        <v>-35.714285714285</v>
       </c>
       <c r="L18" s="15">
-        <v>0</v>
+        <v>-10</v>
       </c>
       <c r="M18" s="13" t="s">
         <v>21</v>
@@ -1070,34 +1070,34 @@
         <v>26</v>
       </c>
       <c r="C19" s="14">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="D19" s="14">
         <v>6</v>
       </c>
       <c r="E19" s="15">
-        <v>33.333333333333</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="F19" s="14">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="G19" s="14">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="H19" s="15">
-        <v>40.740740740740</v>
+        <v>25</v>
       </c>
       <c r="I19" s="14">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="J19" s="14">
-        <v>112</v>
+        <v>118</v>
       </c>
       <c r="K19" s="15">
-        <v>1.785714285714</v>
+        <v>-0.847457627118</v>
       </c>
       <c r="L19" s="15">
-        <v>11.764705882352</v>
+        <v>9.345794392523</v>
       </c>
       <c r="M19" s="13" t="s">
         <v>21</v>
@@ -1110,8 +1110,8 @@
       <c r="A20" s="13" t="s">
         <v>27</v>
       </c>
-      <c r="C20" s="14">
-        <v>1</v>
+      <c r="C20" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D20" s="13" t="s">
         <v>20</v>
@@ -1120,7 +1120,7 @@
         <v>21</v>
       </c>
       <c r="F20" s="14">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G20" s="13" t="s">
         <v>20</v>
@@ -1138,7 +1138,7 @@
         <v>-10</v>
       </c>
       <c r="L20" s="15">
-        <v>20</v>
+        <v>12.5</v>
       </c>
       <c r="M20" s="13" t="s">
         <v>21</v>
@@ -1152,34 +1152,34 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="D21" s="17">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="E21" s="18">
-        <v>66.666666666666</v>
+        <v>-40</v>
       </c>
       <c r="F21" s="17">
-        <v>83</v>
+        <v>73</v>
       </c>
       <c r="G21" s="17">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="H21" s="18">
-        <v>56.603773584905</v>
+        <v>32.727272727272</v>
       </c>
       <c r="I21" s="17">
-        <v>260</v>
+        <v>269</v>
       </c>
       <c r="J21" s="17">
-        <v>243</v>
+        <v>258</v>
       </c>
       <c r="K21" s="18">
-        <v>6.995884773662</v>
+        <v>4.263565891472</v>
       </c>
       <c r="L21" s="18">
-        <v>14.537444933920</v>
+        <v>12.552301255230</v>
       </c>
       <c r="M21" s="19" t="s">
         <v>21</v>
@@ -1233,14 +1233,14 @@
       <c r="A23" s="13" t="s">
         <v>30</v>
       </c>
-      <c r="C23" s="14">
-        <v>1</v>
-      </c>
-      <c r="D23" s="14">
-        <v>2</v>
-      </c>
-      <c r="E23" s="15">
-        <v>-50</v>
+      <c r="C23" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D23" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E23" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F23" s="14">
         <v>1</v>
@@ -1275,34 +1275,34 @@
         <v>31</v>
       </c>
       <c r="C24" s="14">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="D24" s="14">
-        <v>41</v>
+        <v>27</v>
       </c>
       <c r="E24" s="15">
-        <v>-53.658536585365</v>
+        <v>-11.111111111111</v>
       </c>
       <c r="F24" s="14">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="G24" s="14">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="H24" s="15">
-        <v>-25.210084033613</v>
+        <v>-25</v>
       </c>
       <c r="I24" s="14">
-        <v>311</v>
+        <v>336</v>
       </c>
       <c r="J24" s="14">
-        <v>455</v>
+        <v>482</v>
       </c>
       <c r="K24" s="15">
-        <v>-31.648351648351</v>
+        <v>-30.290456431535</v>
       </c>
       <c r="L24" s="15">
-        <v>-33.547008547008</v>
+        <v>-30.721649484536</v>
       </c>
       <c r="M24" s="13" t="s">
         <v>21</v>
@@ -1316,34 +1316,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="14">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="D25" s="14">
-        <v>32</v>
+        <v>17</v>
       </c>
       <c r="E25" s="15">
-        <v>-59.375</v>
+        <v>11.764705882352</v>
       </c>
       <c r="F25" s="14">
-        <v>43</v>
+        <v>53</v>
       </c>
       <c r="G25" s="14">
-        <v>80</v>
+        <v>72</v>
       </c>
       <c r="H25" s="15">
-        <v>-46.25</v>
+        <v>-26.388888888888</v>
       </c>
       <c r="I25" s="14">
-        <v>203</v>
+        <v>222</v>
       </c>
       <c r="J25" s="14">
-        <v>307</v>
+        <v>324</v>
       </c>
       <c r="K25" s="15">
-        <v>-33.876221498371</v>
+        <v>-31.481481481481</v>
       </c>
       <c r="L25" s="15">
-        <v>-37.345679012345</v>
+        <v>-33.731343283582</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1357,34 +1357,34 @@
         <v>33</v>
       </c>
       <c r="C26" s="14">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="D26" s="14">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E26" s="15">
-        <v>-52.631578947368</v>
+        <v>-72.222222222222</v>
       </c>
       <c r="F26" s="14">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="G26" s="14">
         <v>63</v>
       </c>
       <c r="H26" s="15">
-        <v>-44.444444444444</v>
+        <v>-52.380952380952</v>
       </c>
       <c r="I26" s="14">
-        <v>154</v>
+        <v>159</v>
       </c>
       <c r="J26" s="14">
-        <v>166</v>
+        <v>184</v>
       </c>
       <c r="K26" s="15">
-        <v>-7.228915662650</v>
+        <v>-13.586956521739</v>
       </c>
       <c r="L26" s="15">
-        <v>-17.647058823529</v>
+        <v>-21.674876847290</v>
       </c>
       <c r="M26" s="13" t="s">
         <v>21</v>
@@ -1400,32 +1400,32 @@
       <c r="C27" s="14">
         <v>1</v>
       </c>
-      <c r="D27" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E27" s="13" t="s">
-        <v>21</v>
+      <c r="D27" s="14">
+        <v>2</v>
+      </c>
+      <c r="E27" s="15">
+        <v>-50</v>
       </c>
       <c r="F27" s="14">
+        <v>2</v>
+      </c>
+      <c r="G27" s="14">
         <v>4</v>
       </c>
-      <c r="G27" s="14">
-        <v>3</v>
-      </c>
       <c r="H27" s="15">
-        <v>33.333333333333</v>
+        <v>-50</v>
       </c>
       <c r="I27" s="14">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J27" s="14">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="K27" s="15">
-        <v>8.333333333333</v>
+        <v>0</v>
       </c>
       <c r="L27" s="15">
-        <v>116.666666666667</v>
+        <v>133.333333333333</v>
       </c>
       <c r="M27" s="13" t="s">
         <v>21</v>
@@ -1451,22 +1451,22 @@
         <v>2</v>
       </c>
       <c r="G28" s="14">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H28" s="15">
-        <v>-50</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="I28" s="14">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J28" s="14">
         <v>19</v>
       </c>
       <c r="K28" s="15">
-        <v>-15.789473684210</v>
+        <v>-10.526315789473</v>
       </c>
       <c r="L28" s="15">
-        <v>14.285714285714</v>
+        <v>13.333333333333</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1479,8 +1479,8 @@
       <c r="A29" s="13" t="s">
         <v>36</v>
       </c>
-      <c r="C29" s="14">
-        <v>1</v>
+      <c r="C29" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D29" s="13" t="s">
         <v>20</v>
@@ -1520,8 +1520,8 @@
       <c r="A30" s="13" t="s">
         <v>37</v>
       </c>
-      <c r="C30" s="14">
-        <v>1</v>
+      <c r="C30" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D30" s="13" t="s">
         <v>20</v>
@@ -1561,8 +1561,8 @@
       <c r="A31" s="13" t="s">
         <v>38</v>
       </c>
-      <c r="C31" s="13" t="s">
-        <v>20</v>
+      <c r="C31" s="14">
+        <v>1</v>
       </c>
       <c r="D31" s="13" t="s">
         <v>20</v>
@@ -1570,8 +1570,8 @@
       <c r="E31" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="F31" s="13" t="s">
-        <v>20</v>
+      <c r="F31" s="14">
+        <v>1</v>
       </c>
       <c r="G31" s="13" t="s">
         <v>20</v>
@@ -1580,7 +1580,7 @@
         <v>21</v>
       </c>
       <c r="I31" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J31" s="13" t="s">
         <v>20</v>
@@ -1589,7 +1589,7 @@
         <v>21</v>
       </c>
       <c r="L31" s="15">
-        <v>-66.666666666666</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="M31" s="13" t="s">
         <v>21</v>

--- a/data/source/weekly/cs-en-us-121pct.xlsx
+++ b/data/source/weekly/cs-en-us-121pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">17</t>
+      <t xml:space="preserve">18</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">4/20/2026</t>
+      <t xml:space="preserve">4/27/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">4/26/2026</t>
+      <t xml:space="preserve">5/3/2026</t>
     </r>
   </si>
   <si>
@@ -909,7 +909,7 @@
         <v>20</v>
       </c>
       <c r="D15" s="14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E15" s="15">
         <v>-100</v>
@@ -918,19 +918,19 @@
         <v>1</v>
       </c>
       <c r="G15" s="14">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H15" s="15">
-        <v>-75</v>
+        <v>-80</v>
       </c>
       <c r="I15" s="14">
         <v>8</v>
       </c>
       <c r="J15" s="14">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K15" s="15">
-        <v>-33.333333333333</v>
+        <v>-38.461538461538</v>
       </c>
       <c r="L15" s="15">
         <v>166.666666666667</v>
@@ -946,35 +946,35 @@
       <c r="A16" s="13" t="s">
         <v>23</v>
       </c>
-      <c r="C16" s="13" t="s">
-        <v>20</v>
+      <c r="C16" s="14">
+        <v>3</v>
       </c>
       <c r="D16" s="14">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E16" s="15">
-        <v>-100</v>
+        <v>200</v>
       </c>
       <c r="F16" s="14">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="G16" s="14">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H16" s="15">
-        <v>0</v>
+        <v>16.666666666666</v>
       </c>
       <c r="I16" s="14">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="J16" s="14">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="K16" s="15">
-        <v>17.647058823529</v>
+        <v>27.777777777777</v>
       </c>
       <c r="L16" s="15">
-        <v>-23.076923076923</v>
+        <v>-17.857142857142</v>
       </c>
       <c r="M16" s="13" t="s">
         <v>21</v>
@@ -988,34 +988,34 @@
         <v>24</v>
       </c>
       <c r="C17" s="14">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="D17" s="14">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="E17" s="15">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="F17" s="14">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="G17" s="14">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="H17" s="15">
-        <v>35.714285714285</v>
+        <v>22.222222222222</v>
       </c>
       <c r="I17" s="14">
-        <v>88</v>
+        <v>98</v>
       </c>
       <c r="J17" s="14">
-        <v>63</v>
+        <v>72</v>
       </c>
       <c r="K17" s="15">
-        <v>39.682539682539</v>
+        <v>36.111111111111</v>
       </c>
       <c r="L17" s="15">
-        <v>31.343283582089</v>
+        <v>36.111111111111</v>
       </c>
       <c r="M17" s="13" t="s">
         <v>21</v>
@@ -1029,34 +1029,34 @@
         <v>25</v>
       </c>
       <c r="C18" s="14">
+        <v>3</v>
+      </c>
+      <c r="D18" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E18" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="F18" s="14">
+        <v>9</v>
+      </c>
+      <c r="G18" s="14">
         <v>2</v>
       </c>
-      <c r="D18" s="14">
-        <v>2</v>
-      </c>
-      <c r="E18" s="15">
-        <v>0</v>
-      </c>
-      <c r="F18" s="14">
-        <v>7</v>
-      </c>
-      <c r="G18" s="14">
-        <v>4</v>
-      </c>
       <c r="H18" s="15">
-        <v>75</v>
+        <v>350</v>
       </c>
       <c r="I18" s="14">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="J18" s="14">
         <v>28</v>
       </c>
       <c r="K18" s="15">
-        <v>-35.714285714285</v>
+        <v>-25</v>
       </c>
       <c r="L18" s="15">
-        <v>-10</v>
+        <v>0</v>
       </c>
       <c r="M18" s="13" t="s">
         <v>21</v>
@@ -1070,34 +1070,34 @@
         <v>26</v>
       </c>
       <c r="C19" s="14">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="D19" s="14">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="E19" s="15">
-        <v>-33.333333333333</v>
+        <v>-25</v>
       </c>
       <c r="F19" s="14">
         <v>35</v>
       </c>
       <c r="G19" s="14">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="H19" s="15">
-        <v>25</v>
+        <v>16.666666666666</v>
       </c>
       <c r="I19" s="14">
-        <v>117</v>
+        <v>127</v>
       </c>
       <c r="J19" s="14">
-        <v>118</v>
+        <v>130</v>
       </c>
       <c r="K19" s="15">
-        <v>-0.847457627118</v>
+        <v>-2.307692307692</v>
       </c>
       <c r="L19" s="15">
-        <v>9.345794392523</v>
+        <v>6.722689075630</v>
       </c>
       <c r="M19" s="13" t="s">
         <v>21</v>
@@ -1110,8 +1110,8 @@
       <c r="A20" s="13" t="s">
         <v>27</v>
       </c>
-      <c r="C20" s="13" t="s">
-        <v>20</v>
+      <c r="C20" s="14">
+        <v>1</v>
       </c>
       <c r="D20" s="13" t="s">
         <v>20</v>
@@ -1120,7 +1120,7 @@
         <v>21</v>
       </c>
       <c r="F20" s="14">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="G20" s="13" t="s">
         <v>20</v>
@@ -1129,16 +1129,16 @@
         <v>21</v>
       </c>
       <c r="I20" s="14">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J20" s="14">
         <v>20</v>
       </c>
       <c r="K20" s="15">
-        <v>-10</v>
+        <v>-5</v>
       </c>
       <c r="L20" s="15">
-        <v>12.5</v>
+        <v>11.764705882352</v>
       </c>
       <c r="M20" s="13" t="s">
         <v>21</v>
@@ -1152,34 +1152,34 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>9</v>
+        <v>25</v>
       </c>
       <c r="D21" s="17">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="E21" s="18">
-        <v>-40</v>
+        <v>8.695652173913</v>
       </c>
       <c r="F21" s="17">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="G21" s="17">
-        <v>55</v>
+        <v>61</v>
       </c>
       <c r="H21" s="18">
-        <v>32.727272727272</v>
+        <v>26.229508196721</v>
       </c>
       <c r="I21" s="17">
-        <v>269</v>
+        <v>296</v>
       </c>
       <c r="J21" s="17">
-        <v>258</v>
+        <v>281</v>
       </c>
       <c r="K21" s="18">
-        <v>4.263565891472</v>
+        <v>5.338078291814</v>
       </c>
       <c r="L21" s="18">
-        <v>12.552301255230</v>
+        <v>13.846153846153</v>
       </c>
       <c r="M21" s="19" t="s">
         <v>21</v>
@@ -1236,29 +1236,29 @@
       <c r="C23" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D23" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E23" s="13" t="s">
-        <v>21</v>
+      <c r="D23" s="14">
+        <v>1</v>
+      </c>
+      <c r="E23" s="15">
+        <v>-100</v>
       </c>
       <c r="F23" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G23" s="14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H23" s="15">
-        <v>-50</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="I23" s="14">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J23" s="14">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K23" s="15">
-        <v>-40</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="L23" s="15">
         <v>0</v>
@@ -1275,34 +1275,34 @@
         <v>31</v>
       </c>
       <c r="C24" s="14">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="D24" s="14">
-        <v>27</v>
+        <v>39</v>
       </c>
       <c r="E24" s="15">
-        <v>-11.111111111111</v>
+        <v>-43.589743589743</v>
       </c>
       <c r="F24" s="14">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="G24" s="14">
-        <v>116</v>
+        <v>127</v>
       </c>
       <c r="H24" s="15">
-        <v>-25</v>
+        <v>-29.133858267716</v>
       </c>
       <c r="I24" s="14">
-        <v>336</v>
+        <v>358</v>
       </c>
       <c r="J24" s="14">
-        <v>482</v>
+        <v>521</v>
       </c>
       <c r="K24" s="15">
-        <v>-30.290456431535</v>
+        <v>-31.285988483685</v>
       </c>
       <c r="L24" s="15">
-        <v>-30.721649484536</v>
+        <v>-29.249011857707</v>
       </c>
       <c r="M24" s="13" t="s">
         <v>21</v>
@@ -1316,34 +1316,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="14">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="D25" s="14">
-        <v>17</v>
+        <v>31</v>
       </c>
       <c r="E25" s="15">
-        <v>11.764705882352</v>
+        <v>-54.838709677419</v>
       </c>
       <c r="F25" s="14">
-        <v>53</v>
+        <v>59</v>
       </c>
       <c r="G25" s="14">
-        <v>72</v>
+        <v>88</v>
       </c>
       <c r="H25" s="15">
-        <v>-26.388888888888</v>
+        <v>-32.954545454545</v>
       </c>
       <c r="I25" s="14">
-        <v>222</v>
+        <v>236</v>
       </c>
       <c r="J25" s="14">
-        <v>324</v>
+        <v>355</v>
       </c>
       <c r="K25" s="15">
-        <v>-31.481481481481</v>
+        <v>-33.521126760563</v>
       </c>
       <c r="L25" s="15">
-        <v>-33.731343283582</v>
+        <v>-32.378223495702</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1357,34 +1357,34 @@
         <v>33</v>
       </c>
       <c r="C26" s="14">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="D26" s="14">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="E26" s="15">
-        <v>-72.222222222222</v>
+        <v>22.222222222222</v>
       </c>
       <c r="F26" s="14">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="G26" s="14">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="H26" s="15">
-        <v>-52.380952380952</v>
+        <v>-47.540983606557</v>
       </c>
       <c r="I26" s="14">
-        <v>159</v>
+        <v>170</v>
       </c>
       <c r="J26" s="14">
-        <v>184</v>
+        <v>193</v>
       </c>
       <c r="K26" s="15">
-        <v>-13.586956521739</v>
+        <v>-11.917098445595</v>
       </c>
       <c r="L26" s="15">
-        <v>-21.674876847290</v>
+        <v>-19.431279620853</v>
       </c>
       <c r="M26" s="13" t="s">
         <v>21</v>
@@ -1397,35 +1397,35 @@
       <c r="A27" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="C27" s="14">
+      <c r="C27" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D27" s="14">
         <v>1</v>
       </c>
-      <c r="D27" s="14">
-        <v>2</v>
-      </c>
       <c r="E27" s="15">
-        <v>-50</v>
+        <v>-100</v>
       </c>
       <c r="F27" s="14">
         <v>2</v>
       </c>
       <c r="G27" s="14">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H27" s="15">
-        <v>-50</v>
+        <v>-60</v>
       </c>
       <c r="I27" s="14">
         <v>14</v>
       </c>
       <c r="J27" s="14">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K27" s="15">
-        <v>0</v>
+        <v>-6.666666666666</v>
       </c>
       <c r="L27" s="15">
-        <v>133.333333333333</v>
+        <v>100</v>
       </c>
       <c r="M27" s="13" t="s">
         <v>21</v>
@@ -1438,14 +1438,14 @@
       <c r="A28" s="13" t="s">
         <v>35</v>
       </c>
-      <c r="C28" s="14">
+      <c r="C28" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D28" s="14">
         <v>1</v>
       </c>
-      <c r="D28" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E28" s="13" t="s">
-        <v>21</v>
+      <c r="E28" s="15">
+        <v>-100</v>
       </c>
       <c r="F28" s="14">
         <v>2</v>
@@ -1460,13 +1460,13 @@
         <v>17</v>
       </c>
       <c r="J28" s="14">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K28" s="15">
-        <v>-10.526315789473</v>
+        <v>-15</v>
       </c>
       <c r="L28" s="15">
-        <v>13.333333333333</v>
+        <v>0</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1489,7 +1489,7 @@
         <v>21</v>
       </c>
       <c r="F29" s="14">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G29" s="13" t="s">
         <v>20</v>
@@ -1498,16 +1498,16 @@
         <v>21</v>
       </c>
       <c r="I29" s="14">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J29" s="14">
         <v>1</v>
       </c>
       <c r="K29" s="15">
-        <v>100</v>
+        <v>300</v>
       </c>
       <c r="L29" s="15">
-        <v>100</v>
+        <v>300</v>
       </c>
       <c r="M29" s="13" t="s">
         <v>21</v>
@@ -1530,7 +1530,7 @@
         <v>21</v>
       </c>
       <c r="F30" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G30" s="13" t="s">
         <v>20</v>
@@ -1539,16 +1539,16 @@
         <v>21</v>
       </c>
       <c r="I30" s="14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J30" s="14">
         <v>1</v>
       </c>
       <c r="K30" s="15">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="L30" s="15">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="M30" s="13" t="s">
         <v>21</v>
@@ -1561,8 +1561,8 @@
       <c r="A31" s="13" t="s">
         <v>38</v>
       </c>
-      <c r="C31" s="14">
-        <v>1</v>
+      <c r="C31" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D31" s="13" t="s">
         <v>20</v>
@@ -1571,7 +1571,7 @@
         <v>21</v>
       </c>
       <c r="F31" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G31" s="13" t="s">
         <v>20</v>
@@ -1580,7 +1580,7 @@
         <v>21</v>
       </c>
       <c r="I31" s="14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J31" s="13" t="s">
         <v>20</v>
@@ -1589,7 +1589,7 @@
         <v>21</v>
       </c>
       <c r="L31" s="15">
-        <v>-33.333333333333</v>
+        <v>0</v>
       </c>
       <c r="M31" s="13" t="s">
         <v>21</v>
@@ -1620,8 +1620,8 @@
       <c r="A33" s="13" t="s">
         <v>40</v>
       </c>
-      <c r="C33" s="13" t="s">
-        <v>20</v>
+      <c r="C33" s="14">
+        <v>1</v>
       </c>
       <c r="D33" s="13" t="s">
         <v>20</v>
@@ -1630,7 +1630,7 @@
         <v>21</v>
       </c>
       <c r="F33" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G33" s="13" t="s">
         <v>20</v>
@@ -1639,7 +1639,7 @@
         <v>21</v>
       </c>
       <c r="I33" s="14">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J33" s="13" t="s">
         <v>20</v>
@@ -1648,7 +1648,7 @@
         <v>21</v>
       </c>
       <c r="L33" s="15">
-        <v>100</v>
+        <v>150</v>
       </c>
       <c r="M33" s="13" t="s">
         <v>21</v>

--- a/data/source/weekly/cs-en-us-121pct.xlsx
+++ b/data/source/weekly/cs-en-us-121pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">18</t>
+      <t xml:space="preserve">19</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">4/27/2026</t>
+      <t xml:space="preserve">5/4/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">5/3/2026</t>
+      <t xml:space="preserve">5/10/2026</t>
     </r>
   </si>
   <si>
@@ -908,20 +908,20 @@
       <c r="C15" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D15" s="14">
-        <v>1</v>
-      </c>
-      <c r="E15" s="15">
-        <v>-100</v>
+      <c r="D15" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E15" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F15" s="14">
         <v>1</v>
       </c>
       <c r="G15" s="14">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="H15" s="15">
-        <v>-80</v>
+        <v>-66.666666666666</v>
       </c>
       <c r="I15" s="14">
         <v>8</v>
@@ -947,34 +947,34 @@
         <v>23</v>
       </c>
       <c r="C16" s="14">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D16" s="14">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E16" s="15">
-        <v>200</v>
+        <v>-50</v>
       </c>
       <c r="F16" s="14">
         <v>7</v>
       </c>
       <c r="G16" s="14">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="H16" s="15">
-        <v>16.666666666666</v>
+        <v>-22.222222222222</v>
       </c>
       <c r="I16" s="14">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="J16" s="14">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="K16" s="15">
-        <v>27.777777777777</v>
+        <v>9.090909090909</v>
       </c>
       <c r="L16" s="15">
-        <v>-17.857142857142</v>
+        <v>-25</v>
       </c>
       <c r="M16" s="13" t="s">
         <v>21</v>
@@ -988,34 +988,34 @@
         <v>24</v>
       </c>
       <c r="C17" s="14">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="D17" s="14">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="E17" s="15">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="F17" s="14">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="G17" s="14">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="H17" s="15">
-        <v>22.222222222222</v>
+        <v>20</v>
       </c>
       <c r="I17" s="14">
-        <v>98</v>
+        <v>103</v>
       </c>
       <c r="J17" s="14">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="K17" s="15">
-        <v>36.111111111111</v>
+        <v>35.526315789473</v>
       </c>
       <c r="L17" s="15">
-        <v>36.111111111111</v>
+        <v>30.379746835443</v>
       </c>
       <c r="M17" s="13" t="s">
         <v>21</v>
@@ -1028,32 +1028,32 @@
       <c r="A18" s="13" t="s">
         <v>25</v>
       </c>
-      <c r="C18" s="14">
+      <c r="C18" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D18" s="14">
+        <v>1</v>
+      </c>
+      <c r="E18" s="15">
+        <v>-100</v>
+      </c>
+      <c r="F18" s="14">
+        <v>7</v>
+      </c>
+      <c r="G18" s="14">
         <v>3</v>
       </c>
-      <c r="D18" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E18" s="13" t="s">
-        <v>21</v>
-      </c>
-      <c r="F18" s="14">
-        <v>9</v>
-      </c>
-      <c r="G18" s="14">
-        <v>2</v>
-      </c>
       <c r="H18" s="15">
-        <v>350</v>
+        <v>133.333333333333</v>
       </c>
       <c r="I18" s="14">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="J18" s="14">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="K18" s="15">
-        <v>-25</v>
+        <v>-24.137931034482</v>
       </c>
       <c r="L18" s="15">
         <v>0</v>
@@ -1070,34 +1070,34 @@
         <v>26</v>
       </c>
       <c r="C19" s="14">
+        <v>5</v>
+      </c>
+      <c r="D19" s="14">
         <v>9</v>
       </c>
-      <c r="D19" s="14">
-        <v>12</v>
-      </c>
       <c r="E19" s="15">
-        <v>-25</v>
+        <v>-44.444444444444</v>
       </c>
       <c r="F19" s="14">
-        <v>35</v>
+        <v>27</v>
       </c>
       <c r="G19" s="14">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="H19" s="15">
-        <v>16.666666666666</v>
+        <v>-18.181818181818</v>
       </c>
       <c r="I19" s="14">
-        <v>127</v>
+        <v>132</v>
       </c>
       <c r="J19" s="14">
-        <v>130</v>
+        <v>139</v>
       </c>
       <c r="K19" s="15">
-        <v>-2.307692307692</v>
+        <v>-5.035971223021</v>
       </c>
       <c r="L19" s="15">
-        <v>6.722689075630</v>
+        <v>2.325581395348</v>
       </c>
       <c r="M19" s="13" t="s">
         <v>21</v>
@@ -1110,35 +1110,35 @@
       <c r="A20" s="13" t="s">
         <v>27</v>
       </c>
-      <c r="C20" s="14">
+      <c r="C20" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D20" s="14">
         <v>1</v>
       </c>
-      <c r="D20" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E20" s="13" t="s">
-        <v>21</v>
+      <c r="E20" s="15">
+        <v>-100</v>
       </c>
       <c r="F20" s="14">
-        <v>3</v>
-      </c>
-      <c r="G20" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="H20" s="13" t="s">
-        <v>21</v>
+        <v>2</v>
+      </c>
+      <c r="G20" s="14">
+        <v>1</v>
+      </c>
+      <c r="H20" s="15">
+        <v>100</v>
       </c>
       <c r="I20" s="14">
         <v>19</v>
       </c>
       <c r="J20" s="14">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K20" s="15">
-        <v>-5</v>
+        <v>-9.523809523809</v>
       </c>
       <c r="L20" s="15">
-        <v>11.764705882352</v>
+        <v>0</v>
       </c>
       <c r="M20" s="13" t="s">
         <v>21</v>
@@ -1152,34 +1152,34 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>25</v>
+        <v>12</v>
       </c>
       <c r="D21" s="17">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="E21" s="18">
-        <v>8.695652173913</v>
+        <v>-36.842105263157</v>
       </c>
       <c r="F21" s="17">
-        <v>77</v>
+        <v>68</v>
       </c>
       <c r="G21" s="17">
-        <v>61</v>
+        <v>69</v>
       </c>
       <c r="H21" s="18">
-        <v>26.229508196721</v>
+        <v>-1.449275362318</v>
       </c>
       <c r="I21" s="17">
-        <v>296</v>
+        <v>308</v>
       </c>
       <c r="J21" s="17">
-        <v>281</v>
+        <v>300</v>
       </c>
       <c r="K21" s="18">
-        <v>5.338078291814</v>
+        <v>2.666666666666</v>
       </c>
       <c r="L21" s="18">
-        <v>13.846153846153</v>
+        <v>8.450704225352</v>
       </c>
       <c r="M21" s="19" t="s">
         <v>21</v>
@@ -1236,11 +1236,11 @@
       <c r="C23" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D23" s="14">
-        <v>1</v>
-      </c>
-      <c r="E23" s="15">
-        <v>-100</v>
+      <c r="D23" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E23" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F23" s="14">
         <v>2</v>
@@ -1275,34 +1275,34 @@
         <v>31</v>
       </c>
       <c r="C24" s="14">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="D24" s="14">
-        <v>39</v>
+        <v>28</v>
       </c>
       <c r="E24" s="15">
-        <v>-43.589743589743</v>
+        <v>-42.857142857142</v>
       </c>
       <c r="F24" s="14">
-        <v>90</v>
+        <v>82</v>
       </c>
       <c r="G24" s="14">
-        <v>127</v>
+        <v>135</v>
       </c>
       <c r="H24" s="15">
-        <v>-29.133858267716</v>
+        <v>-39.259259259259</v>
       </c>
       <c r="I24" s="14">
-        <v>358</v>
+        <v>374</v>
       </c>
       <c r="J24" s="14">
-        <v>521</v>
+        <v>549</v>
       </c>
       <c r="K24" s="15">
-        <v>-31.285988483685</v>
+        <v>-31.876138433515</v>
       </c>
       <c r="L24" s="15">
-        <v>-29.249011857707</v>
+        <v>-29.566854990583</v>
       </c>
       <c r="M24" s="13" t="s">
         <v>21</v>
@@ -1316,34 +1316,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="14">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="D25" s="14">
-        <v>31</v>
+        <v>18</v>
       </c>
       <c r="E25" s="15">
-        <v>-54.838709677419</v>
+        <v>-50</v>
       </c>
       <c r="F25" s="14">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="G25" s="14">
-        <v>88</v>
+        <v>98</v>
       </c>
       <c r="H25" s="15">
-        <v>-32.954545454545</v>
+        <v>-43.877551020408</v>
       </c>
       <c r="I25" s="14">
-        <v>236</v>
+        <v>245</v>
       </c>
       <c r="J25" s="14">
-        <v>355</v>
+        <v>373</v>
       </c>
       <c r="K25" s="15">
-        <v>-33.521126760563</v>
+        <v>-34.316353887399</v>
       </c>
       <c r="L25" s="15">
-        <v>-32.378223495702</v>
+        <v>-33.604336043360</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1357,34 +1357,34 @@
         <v>33</v>
       </c>
       <c r="C26" s="14">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D26" s="14">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="E26" s="15">
-        <v>22.222222222222</v>
+        <v>-41.176470588235</v>
       </c>
       <c r="F26" s="14">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="G26" s="14">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="H26" s="15">
-        <v>-47.540983606557</v>
+        <v>-44.444444444444</v>
       </c>
       <c r="I26" s="14">
-        <v>170</v>
+        <v>180</v>
       </c>
       <c r="J26" s="14">
-        <v>193</v>
+        <v>210</v>
       </c>
       <c r="K26" s="15">
-        <v>-11.917098445595</v>
+        <v>-14.285714285714</v>
       </c>
       <c r="L26" s="15">
-        <v>-19.431279620853</v>
+        <v>-18.918918918918</v>
       </c>
       <c r="M26" s="13" t="s">
         <v>21</v>
@@ -1400,20 +1400,20 @@
       <c r="C27" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D27" s="14">
-        <v>1</v>
-      </c>
-      <c r="E27" s="15">
-        <v>-100</v>
+      <c r="D27" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E27" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F27" s="14">
         <v>2</v>
       </c>
       <c r="G27" s="14">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="H27" s="15">
-        <v>-60</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="I27" s="14">
         <v>14</v>
@@ -1438,35 +1438,35 @@
       <c r="A28" s="13" t="s">
         <v>35</v>
       </c>
-      <c r="C28" s="13" t="s">
-        <v>20</v>
+      <c r="C28" s="14">
+        <v>1</v>
       </c>
       <c r="D28" s="14">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E28" s="15">
-        <v>-100</v>
+        <v>-66.666666666666</v>
       </c>
       <c r="F28" s="14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G28" s="14">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H28" s="15">
-        <v>-33.333333333333</v>
+        <v>-25</v>
       </c>
       <c r="I28" s="14">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J28" s="14">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="K28" s="15">
-        <v>-15</v>
+        <v>-21.739130434782</v>
       </c>
       <c r="L28" s="15">
-        <v>0</v>
+        <v>-5.263157894736</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1561,8 +1561,8 @@
       <c r="A31" s="13" t="s">
         <v>38</v>
       </c>
-      <c r="C31" s="13" t="s">
-        <v>20</v>
+      <c r="C31" s="14">
+        <v>1</v>
       </c>
       <c r="D31" s="13" t="s">
         <v>20</v>
@@ -1571,7 +1571,7 @@
         <v>21</v>
       </c>
       <c r="F31" s="14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G31" s="13" t="s">
         <v>20</v>
@@ -1580,7 +1580,7 @@
         <v>21</v>
       </c>
       <c r="I31" s="14">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J31" s="13" t="s">
         <v>20</v>
@@ -1589,7 +1589,7 @@
         <v>21</v>
       </c>
       <c r="L31" s="15">
-        <v>0</v>
+        <v>33.333333333333</v>
       </c>
       <c r="M31" s="13" t="s">
         <v>21</v>
@@ -1620,18 +1620,18 @@
       <c r="A33" s="13" t="s">
         <v>40</v>
       </c>
-      <c r="C33" s="14">
+      <c r="C33" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D33" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E33" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="F33" s="14">
         <v>1</v>
       </c>
-      <c r="D33" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E33" s="13" t="s">
-        <v>21</v>
-      </c>
-      <c r="F33" s="14">
-        <v>2</v>
-      </c>
       <c r="G33" s="13" t="s">
         <v>20</v>
       </c>
@@ -1639,7 +1639,7 @@
         <v>21</v>
       </c>
       <c r="I33" s="14">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J33" s="13" t="s">
         <v>20</v>
@@ -1648,7 +1648,7 @@
         <v>21</v>
       </c>
       <c r="L33" s="15">
-        <v>150</v>
+        <v>100</v>
       </c>
       <c r="M33" s="13" t="s">
         <v>21</v>
